--- a/research/traditional_assets/database/data/romania/romania_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_r_e_i_t.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08224646638905236</v>
+        <v>0.08215267204282987</v>
       </c>
       <c r="C2">
-        <v>13.09703171189477</v>
+        <v>12.99811058647589</v>
       </c>
       <c r="D2">
-        <v>13.09703171189477</v>
+        <v>13.12745058647589</v>
       </c>
       <c r="E2">
-        <v>-0.434</v>
+        <v>-0.30466</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.12934</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1439,28 +1439,28 @@
         <v>0.707</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006505801999999999</v>
       </c>
       <c r="N2">
-        <v>0.707</v>
+        <v>0.700494198</v>
       </c>
       <c r="O2">
-        <v>0.11312</v>
+        <v>0.11207907168</v>
       </c>
       <c r="P2">
-        <v>0.59388</v>
+        <v>0.58841512632</v>
       </c>
       <c r="Q2">
-        <v>0.60988</v>
+        <v>0.6044151263200001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08224646638905236</v>
+        <v>0.0825557091341716</v>
       </c>
       <c r="T2">
-        <v>0.5016993284768603</v>
+        <v>0.5059561712639367</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>108.6722282663998</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08215267204282987</v>
+        <v>0.0820588776966074</v>
       </c>
       <c r="C3">
-        <v>12.99811058647589</v>
+        <v>12.89933109040539</v>
       </c>
       <c r="D3">
-        <v>13.12745058647589</v>
+        <v>13.15801109040539</v>
       </c>
       <c r="E3">
-        <v>-0.30466</v>
+        <v>-0.17532</v>
       </c>
       <c r="F3">
-        <v>0.12934</v>
+        <v>0.25868</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1521,28 +1521,28 @@
         <v>0.707</v>
       </c>
       <c r="M3">
-        <v>0.006505801999999999</v>
+        <v>0.013011604</v>
       </c>
       <c r="N3">
-        <v>0.700494198</v>
+        <v>0.693988396</v>
       </c>
       <c r="O3">
-        <v>0.11207907168</v>
+        <v>0.11103814336</v>
       </c>
       <c r="P3">
-        <v>0.58841512632</v>
+        <v>0.58295025264</v>
       </c>
       <c r="Q3">
-        <v>0.6044151263200001</v>
+        <v>0.59895025264</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0825557091341716</v>
+        <v>0.08287126295572184</v>
       </c>
       <c r="T3">
-        <v>0.5059561712639367</v>
+        <v>0.5102998883936064</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>108.6722282663998</v>
+        <v>54.33611413319988</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0820588776966074</v>
+        <v>0.08196508335038491</v>
       </c>
       <c r="C4">
-        <v>12.89933109040539</v>
+        <v>12.80069421512418</v>
       </c>
       <c r="D4">
-        <v>13.15801109040539</v>
+        <v>13.18871421512418</v>
       </c>
       <c r="E4">
-        <v>-0.17532</v>
+        <v>-0.04598000000000002</v>
       </c>
       <c r="F4">
-        <v>0.25868</v>
+        <v>0.38802</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1603,28 +1603,28 @@
         <v>0.707</v>
       </c>
       <c r="M4">
-        <v>0.013011604</v>
+        <v>0.019517406</v>
       </c>
       <c r="N4">
-        <v>0.693988396</v>
+        <v>0.687482594</v>
       </c>
       <c r="O4">
-        <v>0.11103814336</v>
+        <v>0.10999721504</v>
       </c>
       <c r="P4">
-        <v>0.58295025264</v>
+        <v>0.57748537896</v>
       </c>
       <c r="Q4">
-        <v>0.59895025264</v>
+        <v>0.59348537896</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08287126295572184</v>
+        <v>0.08319332304163393</v>
       </c>
       <c r="T4">
-        <v>0.5102998883936064</v>
+        <v>0.5147331667012075</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.33611413319988</v>
+        <v>36.22407608879992</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08196508335038491</v>
+        <v>0.08187128900416242</v>
       </c>
       <c r="C5">
-        <v>12.80069421512418</v>
+        <v>12.7022009613486</v>
       </c>
       <c r="D5">
-        <v>13.18871421512418</v>
+        <v>13.2195609613486</v>
       </c>
       <c r="E5">
-        <v>-0.04598000000000002</v>
+        <v>0.08335999999999993</v>
       </c>
       <c r="F5">
-        <v>0.38802</v>
+        <v>0.5173599999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         <v>0.707</v>
       </c>
       <c r="M5">
-        <v>0.019517406</v>
+        <v>0.026023208</v>
       </c>
       <c r="N5">
-        <v>0.687482594</v>
+        <v>0.6809767919999999</v>
       </c>
       <c r="O5">
-        <v>0.10999721504</v>
+        <v>0.10895628672</v>
       </c>
       <c r="P5">
-        <v>0.57748537896</v>
+        <v>0.5720205052799999</v>
       </c>
       <c r="Q5">
-        <v>0.59348537896</v>
+        <v>0.5880205052799999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08319332304163393</v>
+        <v>0.08352209271266919</v>
       </c>
       <c r="T5">
-        <v>0.5147331667012075</v>
+        <v>0.5192588049735504</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.22407608879992</v>
+        <v>27.16805706659994</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08187128900416242</v>
+        <v>0.08177749465793994</v>
       </c>
       <c r="C6">
-        <v>12.7022009613486</v>
+        <v>12.60385233917916</v>
       </c>
       <c r="D6">
-        <v>13.2195609613486</v>
+        <v>13.25055233917916</v>
       </c>
       <c r="E6">
-        <v>0.08335999999999993</v>
+        <v>0.2127000000000001</v>
       </c>
       <c r="F6">
-        <v>0.5173599999999999</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1767,28 +1767,28 @@
         <v>0.707</v>
       </c>
       <c r="M6">
-        <v>0.026023208</v>
+        <v>0.03252901</v>
       </c>
       <c r="N6">
-        <v>0.6809767919999999</v>
+        <v>0.67447099</v>
       </c>
       <c r="O6">
-        <v>0.10895628672</v>
+        <v>0.1079153584</v>
       </c>
       <c r="P6">
-        <v>0.5720205052799999</v>
+        <v>0.5665556316</v>
       </c>
       <c r="Q6">
-        <v>0.5880205052799999</v>
+        <v>0.5825556316</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08352209271266919</v>
+        <v>0.08385778385046309</v>
       </c>
       <c r="T6">
-        <v>0.5192588049735504</v>
+        <v>0.5238797198411004</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.16805706659994</v>
+        <v>21.73444565327994</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08177749465793994</v>
+        <v>0.08168370031171746</v>
       </c>
       <c r="C7">
-        <v>12.60385233917916</v>
+        <v>12.50564936821074</v>
       </c>
       <c r="D7">
-        <v>13.25055233917916</v>
+        <v>13.28168936821074</v>
       </c>
       <c r="E7">
-        <v>0.2127000000000001</v>
+        <v>0.3420400000000001</v>
       </c>
       <c r="F7">
-        <v>0.6467000000000001</v>
+        <v>0.7760400000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1849,28 +1849,28 @@
         <v>0.707</v>
       </c>
       <c r="M7">
-        <v>0.03252901</v>
+        <v>0.039034812</v>
       </c>
       <c r="N7">
-        <v>0.67447099</v>
+        <v>0.6679651879999999</v>
       </c>
       <c r="O7">
-        <v>0.1079153584</v>
+        <v>0.10687443008</v>
       </c>
       <c r="P7">
-        <v>0.5665556316</v>
+        <v>0.56109075792</v>
       </c>
       <c r="Q7">
-        <v>0.5825556316</v>
+        <v>0.57709075792</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08385778385046309</v>
+        <v>0.08420061735289092</v>
       </c>
       <c r="T7">
-        <v>0.5238797198411004</v>
+        <v>0.528598952046258</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.73444565327994</v>
+        <v>18.11203804439996</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08168370031171746</v>
+        <v>0.08158990596549498</v>
       </c>
       <c r="C8">
-        <v>12.50564936821074</v>
+        <v>12.40759307764447</v>
       </c>
       <c r="D8">
-        <v>13.28168936821074</v>
+        <v>13.31297307764447</v>
       </c>
       <c r="E8">
-        <v>0.34204</v>
+        <v>0.4713799999999999</v>
       </c>
       <c r="F8">
-        <v>0.77604</v>
+        <v>0.9053799999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1931,28 +1931,28 @@
         <v>0.707</v>
       </c>
       <c r="M8">
-        <v>0.039034812</v>
+        <v>0.04554061399999999</v>
       </c>
       <c r="N8">
-        <v>0.6679651879999999</v>
+        <v>0.661459386</v>
       </c>
       <c r="O8">
-        <v>0.10687443008</v>
+        <v>0.10583350176</v>
       </c>
       <c r="P8">
-        <v>0.56109075792</v>
+        <v>0.5556258842399999</v>
       </c>
       <c r="Q8">
-        <v>0.57709075792</v>
+        <v>0.5716258842399999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08420061735289092</v>
+        <v>0.0845508236188118</v>
       </c>
       <c r="T8">
-        <v>0.528598952046258</v>
+        <v>0.5334196731160424</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.11203804439996</v>
+        <v>15.52460403805711</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08158990596549497</v>
+        <v>0.0814961116192725</v>
       </c>
       <c r="C9">
-        <v>12.40759307764447</v>
+        <v>12.30968450640108</v>
       </c>
       <c r="D9">
-        <v>13.31297307764447</v>
+        <v>13.34440450640108</v>
       </c>
       <c r="E9">
-        <v>0.4713800000000001</v>
+        <v>0.6007199999999999</v>
       </c>
       <c r="F9">
-        <v>0.9053800000000001</v>
+        <v>1.03472</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2013,28 +2013,28 @@
         <v>0.707</v>
       </c>
       <c r="M9">
-        <v>0.045540614</v>
+        <v>0.05204641599999999</v>
       </c>
       <c r="N9">
-        <v>0.661459386</v>
+        <v>0.6549535839999999</v>
       </c>
       <c r="O9">
-        <v>0.10583350176</v>
+        <v>0.10479257344</v>
       </c>
       <c r="P9">
-        <v>0.5556258842399999</v>
+        <v>0.5501610105599999</v>
       </c>
       <c r="Q9">
-        <v>0.5716258842399999</v>
+        <v>0.5661610105599999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0845508236188118</v>
+        <v>0.08490864306442662</v>
       </c>
       <c r="T9">
-        <v>0.5334196731160424</v>
+        <v>0.5383451924699527</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.52460403805711</v>
+        <v>13.58402853329997</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0814961116192725</v>
+        <v>0.08151571727305</v>
       </c>
       <c r="C10">
-        <v>12.30968450640108</v>
+        <v>12.17376219141275</v>
       </c>
       <c r="D10">
-        <v>13.34440450640108</v>
+        <v>13.33782219141275</v>
       </c>
       <c r="E10">
-        <v>0.6007199999999999</v>
+        <v>0.7300599999999999</v>
       </c>
       <c r="F10">
-        <v>1.03472</v>
+        <v>1.16406</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2095,45 +2095,45 @@
         <v>0.707</v>
       </c>
       <c r="M10">
-        <v>0.05204641599999999</v>
+        <v>0.06029830799999999</v>
       </c>
       <c r="N10">
-        <v>0.6549535839999999</v>
+        <v>0.6467016919999999</v>
       </c>
       <c r="O10">
-        <v>0.10479257344</v>
+        <v>0.10347227072</v>
       </c>
       <c r="P10">
-        <v>0.5501610105599999</v>
+        <v>0.54322942128</v>
       </c>
       <c r="Q10">
-        <v>0.5661610105599999</v>
+        <v>0.55922942128</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08490864306442662</v>
+        <v>0.08527432667368132</v>
       </c>
       <c r="T10">
-        <v>0.5383451924699527</v>
+        <v>0.5433789649964763</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.16</v>
       </c>
       <c r="W10">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.58402853329997</v>
+        <v>11.72503878549959</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08151571727305</v>
+        <v>0.08143452292682753</v>
       </c>
       <c r="C11">
-        <v>12.17376219141275</v>
+        <v>12.07172434634174</v>
       </c>
       <c r="D11">
-        <v>13.33782219141275</v>
+        <v>13.36512434634174</v>
       </c>
       <c r="E11">
-        <v>0.7300599999999999</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="F11">
-        <v>1.16406</v>
+        <v>1.2934</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2177,28 +2177,28 @@
         <v>0.707</v>
       </c>
       <c r="M11">
-        <v>0.06029830799999999</v>
+        <v>0.06699811999999999</v>
       </c>
       <c r="N11">
-        <v>0.6467016919999999</v>
+        <v>0.64000188</v>
       </c>
       <c r="O11">
-        <v>0.10347227072</v>
+        <v>0.1024003008</v>
       </c>
       <c r="P11">
-        <v>0.54322942128</v>
+        <v>0.5376015792</v>
       </c>
       <c r="Q11">
-        <v>0.55922942128</v>
+        <v>0.5536015792</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08527432667368132</v>
+        <v>0.08564813658536391</v>
       </c>
       <c r="T11">
-        <v>0.5433789649964763</v>
+        <v>0.5485245991347005</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.72503878549959</v>
+        <v>10.55253490694963</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08143452292682753</v>
+        <v>0.08151040858060503</v>
       </c>
       <c r="C12">
-        <v>12.07172434634174</v>
+        <v>11.9168638670127</v>
       </c>
       <c r="D12">
-        <v>13.36512434634174</v>
+        <v>13.3396038670127</v>
       </c>
       <c r="E12">
-        <v>0.8594000000000002</v>
+        <v>0.98874</v>
       </c>
       <c r="F12">
-        <v>1.2934</v>
+        <v>1.42274</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2259,45 +2259,45 @@
         <v>0.707</v>
       </c>
       <c r="M12">
-        <v>0.06699812000000001</v>
+        <v>0.07611659</v>
       </c>
       <c r="N12">
-        <v>0.6400018799999999</v>
+        <v>0.6308834099999999</v>
       </c>
       <c r="O12">
-        <v>0.1024003008</v>
+        <v>0.1009413456</v>
       </c>
       <c r="P12">
-        <v>0.5376015792</v>
+        <v>0.5299420643999999</v>
       </c>
       <c r="Q12">
-        <v>0.5536015792</v>
+        <v>0.5459420643999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08564813658536391</v>
+        <v>0.08603034671978094</v>
       </c>
       <c r="T12">
-        <v>0.5485245991347005</v>
+        <v>0.55378586550075</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.16</v>
       </c>
       <c r="W12">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.55253490694963</v>
+        <v>9.288382466949715</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08151040858060503</v>
+        <v>0.08144349423438256</v>
       </c>
       <c r="C13">
-        <v>11.9168638670127</v>
+        <v>11.81002219124605</v>
       </c>
       <c r="D13">
-        <v>13.3396038670127</v>
+        <v>13.36210219124605</v>
       </c>
       <c r="E13">
-        <v>0.98874</v>
+        <v>1.11808</v>
       </c>
       <c r="F13">
-        <v>1.42274</v>
+        <v>1.55208</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2341,28 +2341,28 @@
         <v>0.707</v>
       </c>
       <c r="M13">
-        <v>0.07611659</v>
+        <v>0.08303627999999999</v>
       </c>
       <c r="N13">
-        <v>0.6308834099999999</v>
+        <v>0.62396372</v>
       </c>
       <c r="O13">
-        <v>0.1009413456</v>
+        <v>0.0998341952</v>
       </c>
       <c r="P13">
-        <v>0.5299420643999999</v>
+        <v>0.5241295248</v>
       </c>
       <c r="Q13">
-        <v>0.5459420643999999</v>
+        <v>0.5401295248</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08603034671978094</v>
+        <v>0.08642124344816199</v>
       </c>
       <c r="T13">
-        <v>0.55378586550075</v>
+        <v>0.5591667061023915</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.288382466949715</v>
+        <v>8.514350594703906</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08144349423438256</v>
+        <v>0.08137657988816008</v>
       </c>
       <c r="C14">
-        <v>11.81002219124605</v>
+        <v>11.70325653418958</v>
       </c>
       <c r="D14">
-        <v>13.36210219124605</v>
+        <v>13.38467653418958</v>
       </c>
       <c r="E14">
-        <v>1.11808</v>
+        <v>1.24742</v>
       </c>
       <c r="F14">
-        <v>1.55208</v>
+        <v>1.68142</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2423,28 +2423,28 @@
         <v>0.707</v>
       </c>
       <c r="M14">
-        <v>0.08303627999999999</v>
+        <v>0.08995597</v>
       </c>
       <c r="N14">
-        <v>0.62396372</v>
+        <v>0.61704403</v>
       </c>
       <c r="O14">
-        <v>0.0998341952</v>
+        <v>0.0987270448</v>
       </c>
       <c r="P14">
-        <v>0.5241295248</v>
+        <v>0.5183169852</v>
       </c>
       <c r="Q14">
-        <v>0.5401295248</v>
+        <v>0.5343169852</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08642124344816199</v>
+        <v>0.08682112630822997</v>
       </c>
       <c r="T14">
-        <v>0.5591667061023915</v>
+        <v>0.5646712441891283</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.514350594703906</v>
+        <v>7.859400548957451</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08137657988816008</v>
+        <v>0.08140374554193759</v>
       </c>
       <c r="C15">
-        <v>11.70325653418958</v>
+        <v>11.56474268989037</v>
       </c>
       <c r="D15">
-        <v>13.38467653418958</v>
+        <v>13.37550268989037</v>
       </c>
       <c r="E15">
-        <v>1.24742</v>
+        <v>1.37676</v>
       </c>
       <c r="F15">
-        <v>1.68142</v>
+        <v>1.81076</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2505,45 +2505,45 @@
         <v>0.707</v>
       </c>
       <c r="M15">
-        <v>0.08995597</v>
+        <v>0.09832426800000001</v>
       </c>
       <c r="N15">
-        <v>0.61704403</v>
+        <v>0.6086757319999999</v>
       </c>
       <c r="O15">
-        <v>0.0987270448</v>
+        <v>0.09738811711999999</v>
       </c>
       <c r="P15">
-        <v>0.5183169852</v>
+        <v>0.51128761488</v>
       </c>
       <c r="Q15">
-        <v>0.5343169852</v>
+        <v>0.52728761488</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08682112630822997</v>
+        <v>0.08723030876969487</v>
       </c>
       <c r="T15">
-        <v>0.5646712441891283</v>
+        <v>0.5703037947895101</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.16</v>
       </c>
       <c r="W15">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.859400548957451</v>
+        <v>7.190493398842286</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08140374554193759</v>
+        <v>0.0813435511957151</v>
       </c>
       <c r="C16">
-        <v>11.56474268989037</v>
+        <v>11.4557472926038</v>
       </c>
       <c r="D16">
-        <v>13.37550268989037</v>
+        <v>13.3958472926038</v>
       </c>
       <c r="E16">
-        <v>1.37676</v>
+        <v>1.5061</v>
       </c>
       <c r="F16">
-        <v>1.81076</v>
+        <v>1.9401</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2587,28 +2587,28 @@
         <v>0.707</v>
       </c>
       <c r="M16">
-        <v>0.09832426800000001</v>
+        <v>0.10534743</v>
       </c>
       <c r="N16">
-        <v>0.6086757319999999</v>
+        <v>0.6016525699999999</v>
       </c>
       <c r="O16">
-        <v>0.09738811711999999</v>
+        <v>0.0962644112</v>
       </c>
       <c r="P16">
-        <v>0.51128761488</v>
+        <v>0.5053881588</v>
       </c>
       <c r="Q16">
-        <v>0.52728761488</v>
+        <v>0.5213881588</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08723030876969487</v>
+        <v>0.08764911905378248</v>
       </c>
       <c r="T16">
-        <v>0.5703037947895101</v>
+        <v>0.5760688759922536</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.190493398842286</v>
+        <v>6.711127172252801</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0813435511957151</v>
+        <v>0.08128335684949262</v>
       </c>
       <c r="C17">
-        <v>11.4557472926038</v>
+        <v>11.34681387928729</v>
       </c>
       <c r="D17">
-        <v>13.3958472926038</v>
+        <v>13.41625387928729</v>
       </c>
       <c r="E17">
-        <v>1.5061</v>
+        <v>1.63544</v>
       </c>
       <c r="F17">
-        <v>1.9401</v>
+        <v>2.06944</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2669,28 +2669,28 @@
         <v>0.707</v>
       </c>
       <c r="M17">
-        <v>0.10534743</v>
+        <v>0.112370592</v>
       </c>
       <c r="N17">
-        <v>0.6016525699999999</v>
+        <v>0.594629408</v>
       </c>
       <c r="O17">
-        <v>0.0962644112</v>
+        <v>0.09514070528</v>
       </c>
       <c r="P17">
-        <v>0.5053881588</v>
+        <v>0.49948870272</v>
       </c>
       <c r="Q17">
-        <v>0.5213881588</v>
+        <v>0.5154887027199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08764911905378248</v>
+        <v>0.08807790101130074</v>
       </c>
       <c r="T17">
-        <v>0.5760688759922536</v>
+        <v>0.5819712210331579</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.711127172252802</v>
+        <v>6.291681723987002</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08128335684949262</v>
+        <v>0.08136596250327013</v>
       </c>
       <c r="C18">
-        <v>11.34681387928729</v>
+        <v>11.18948544748378</v>
       </c>
       <c r="D18">
-        <v>13.41625387928729</v>
+        <v>13.38826544748378</v>
       </c>
       <c r="E18">
-        <v>1.63544</v>
+        <v>1.76478</v>
       </c>
       <c r="F18">
-        <v>2.06944</v>
+        <v>2.19878</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2751,45 +2751,45 @@
         <v>0.707</v>
       </c>
       <c r="M18">
-        <v>0.112370592</v>
+        <v>0.121592534</v>
       </c>
       <c r="N18">
-        <v>0.594629408</v>
+        <v>0.5854074659999999</v>
       </c>
       <c r="O18">
-        <v>0.09514070528</v>
+        <v>0.09366519456</v>
       </c>
       <c r="P18">
-        <v>0.49948870272</v>
+        <v>0.4917422714399999</v>
       </c>
       <c r="Q18">
-        <v>0.5154887027199999</v>
+        <v>0.5077422714399999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08807790101130074</v>
+        <v>0.08851701506418089</v>
       </c>
       <c r="T18">
-        <v>0.5819712210331579</v>
+        <v>0.5880157912557707</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.16</v>
       </c>
       <c r="W18">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.291681723987002</v>
+        <v>5.81450173577269</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08136596250327013</v>
+        <v>0.08131416815704764</v>
       </c>
       <c r="C19">
-        <v>11.18948544748378</v>
+        <v>11.07768072485019</v>
       </c>
       <c r="D19">
-        <v>13.38826544748378</v>
+        <v>13.40580072485019</v>
       </c>
       <c r="E19">
-        <v>1.76478</v>
+        <v>1.89412</v>
       </c>
       <c r="F19">
-        <v>2.19878</v>
+        <v>2.32812</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2833,28 +2833,28 @@
         <v>0.707</v>
       </c>
       <c r="M19">
-        <v>0.121592534</v>
+        <v>0.128745036</v>
       </c>
       <c r="N19">
-        <v>0.5854074659999999</v>
+        <v>0.578254964</v>
       </c>
       <c r="O19">
-        <v>0.09366519456</v>
+        <v>0.09252079424</v>
       </c>
       <c r="P19">
-        <v>0.4917422714399999</v>
+        <v>0.48573416976</v>
       </c>
       <c r="Q19">
-        <v>0.5077422714399999</v>
+        <v>0.50173416976</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08851701506418089</v>
+        <v>0.08896683921591177</v>
       </c>
       <c r="T19">
-        <v>0.5880157912557707</v>
+        <v>0.5942077900203984</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.81450173577269</v>
+        <v>5.491473861563097</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08131416815704766</v>
+        <v>0.08126237381082516</v>
       </c>
       <c r="C20">
-        <v>11.07768072485018</v>
+        <v>10.96592199610749</v>
       </c>
       <c r="D20">
-        <v>13.40580072485018</v>
+        <v>13.42338199610749</v>
       </c>
       <c r="E20">
-        <v>1.89412</v>
+        <v>2.02346</v>
       </c>
       <c r="F20">
-        <v>2.32812</v>
+        <v>2.45746</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2915,28 +2915,28 @@
         <v>0.707</v>
       </c>
       <c r="M20">
-        <v>0.128745036</v>
+        <v>0.135897538</v>
       </c>
       <c r="N20">
-        <v>0.578254964</v>
+        <v>0.571102462</v>
       </c>
       <c r="O20">
-        <v>0.09252079424</v>
+        <v>0.09137639392000001</v>
       </c>
       <c r="P20">
-        <v>0.48573416976</v>
+        <v>0.47972606808</v>
       </c>
       <c r="Q20">
-        <v>0.50173416976</v>
+        <v>0.49572606808</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08896683921591177</v>
+        <v>0.08942777013682118</v>
       </c>
       <c r="T20">
-        <v>0.5942077900203984</v>
+        <v>0.6005526776434119</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.491473861563098</v>
+        <v>5.20244892148083</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08126237381082516</v>
+        <v>0.08121057946460271</v>
       </c>
       <c r="C21">
-        <v>10.96592199610749</v>
+        <v>10.85420944245178</v>
       </c>
       <c r="D21">
-        <v>13.42338199610749</v>
+        <v>13.44100944245178</v>
       </c>
       <c r="E21">
-        <v>2.02346</v>
+        <v>2.1528</v>
       </c>
       <c r="F21">
-        <v>2.45746</v>
+        <v>2.5868</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2997,28 +2997,28 @@
         <v>0.707</v>
       </c>
       <c r="M21">
-        <v>0.135897538</v>
+        <v>0.14305004</v>
       </c>
       <c r="N21">
-        <v>0.571102462</v>
+        <v>0.56394996</v>
       </c>
       <c r="O21">
-        <v>0.09137639392000001</v>
+        <v>0.09023199359999999</v>
       </c>
       <c r="P21">
-        <v>0.47972606808</v>
+        <v>0.4737179664</v>
       </c>
       <c r="Q21">
-        <v>0.49572606808</v>
+        <v>0.4897179664</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08942777013682118</v>
+        <v>0.08990022433075337</v>
       </c>
       <c r="T21">
-        <v>0.6005526776434119</v>
+        <v>0.607056187457001</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.20244892148083</v>
+        <v>4.942326475406787</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08121057946460271</v>
+        <v>0.08115878511838021</v>
       </c>
       <c r="C22">
-        <v>10.85420944245178</v>
+        <v>10.74254324603223</v>
       </c>
       <c r="D22">
-        <v>13.44100944245178</v>
+        <v>13.45868324603223</v>
       </c>
       <c r="E22">
-        <v>2.1528</v>
+        <v>2.28214</v>
       </c>
       <c r="F22">
-        <v>2.5868</v>
+        <v>2.71614</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3079,28 +3079,28 @@
         <v>0.707</v>
       </c>
       <c r="M22">
-        <v>0.14305004</v>
+        <v>0.150202542</v>
       </c>
       <c r="N22">
-        <v>0.56394996</v>
+        <v>0.5567974579999999</v>
       </c>
       <c r="O22">
-        <v>0.09023199359999999</v>
+        <v>0.08908759327999999</v>
       </c>
       <c r="P22">
-        <v>0.4737179664</v>
+        <v>0.4677098647199999</v>
       </c>
       <c r="Q22">
-        <v>0.4897179664</v>
+        <v>0.4837098647199999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08990022433075337</v>
+        <v>0.09038463939035468</v>
       </c>
       <c r="T22">
-        <v>0.607056187457001</v>
+        <v>0.6137243430886554</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.942326475406787</v>
+        <v>4.706977595625511</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08115878511838021</v>
+        <v>0.08156899077215772</v>
       </c>
       <c r="C23">
-        <v>10.74254324603223</v>
+        <v>10.47448913507802</v>
       </c>
       <c r="D23">
-        <v>13.45868324603223</v>
+        <v>13.31996913507802</v>
       </c>
       <c r="E23">
-        <v>2.28214</v>
+        <v>2.41148</v>
       </c>
       <c r="F23">
-        <v>2.71614</v>
+        <v>2.84548</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3161,45 +3161,45 @@
         <v>0.707</v>
       </c>
       <c r="M23">
-        <v>0.150202542</v>
+        <v>0.164468744</v>
       </c>
       <c r="N23">
-        <v>0.5567974579999999</v>
+        <v>0.542531256</v>
       </c>
       <c r="O23">
-        <v>0.08908759327999999</v>
+        <v>0.08680500095999999</v>
       </c>
       <c r="P23">
-        <v>0.4677098647199999</v>
+        <v>0.45572625504</v>
       </c>
       <c r="Q23">
-        <v>0.4837098647199999</v>
+        <v>0.47172625504</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09038463939035468</v>
+        <v>0.09088147534892015</v>
       </c>
       <c r="T23">
-        <v>0.6137243430886554</v>
+        <v>0.6205634770698394</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.16</v>
       </c>
       <c r="W23">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.706977595625512</v>
+        <v>4.298689117489703</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08156899077215772</v>
+        <v>0.08153819642593524</v>
       </c>
       <c r="C24">
-        <v>10.47448913507802</v>
+        <v>10.35546312709208</v>
       </c>
       <c r="D24">
-        <v>13.31996913507802</v>
+        <v>13.33028312709208</v>
       </c>
       <c r="E24">
-        <v>2.41148</v>
+        <v>2.54082</v>
       </c>
       <c r="F24">
-        <v>2.84548</v>
+        <v>2.97482</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         <v>0.707</v>
       </c>
       <c r="M24">
-        <v>0.164468744</v>
+        <v>0.171944596</v>
       </c>
       <c r="N24">
-        <v>0.542531256</v>
+        <v>0.535055404</v>
       </c>
       <c r="O24">
-        <v>0.08680500095999999</v>
+        <v>0.08560886463999999</v>
       </c>
       <c r="P24">
-        <v>0.45572625504</v>
+        <v>0.44944653936</v>
       </c>
       <c r="Q24">
-        <v>0.47172625504</v>
+        <v>0.46544653936</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09088147534892015</v>
+        <v>0.09139121613757822</v>
       </c>
       <c r="T24">
-        <v>0.6205634770698394</v>
+        <v>0.6275802508946907</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.298689117489703</v>
+        <v>4.111789590642324</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08153819642593524</v>
+        <v>0.08221300207971274</v>
       </c>
       <c r="C25">
-        <v>10.35546312709208</v>
+        <v>10.00370848626158</v>
       </c>
       <c r="D25">
-        <v>13.33028312709208</v>
+        <v>13.10786848626158</v>
       </c>
       <c r="E25">
-        <v>2.54082</v>
+        <v>2.67016</v>
       </c>
       <c r="F25">
-        <v>2.97482</v>
+        <v>3.10416</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3325,45 +3325,45 @@
         <v>0.707</v>
       </c>
       <c r="M25">
-        <v>0.171944596</v>
+        <v>0.190285008</v>
       </c>
       <c r="N25">
-        <v>0.535055404</v>
+        <v>0.5167149919999999</v>
       </c>
       <c r="O25">
-        <v>0.08560886463999999</v>
+        <v>0.08267439871999999</v>
       </c>
       <c r="P25">
-        <v>0.44944653936</v>
+        <v>0.4340405932799999</v>
       </c>
       <c r="Q25">
-        <v>0.46544653936</v>
+        <v>0.45004059328</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09139121613757822</v>
+        <v>0.09191437115751677</v>
       </c>
       <c r="T25">
-        <v>0.6275802508946907</v>
+        <v>0.6347816766623011</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.16</v>
       </c>
       <c r="W25">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.111789590642324</v>
+        <v>3.715479256253335</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08221300207971274</v>
+        <v>0.08221160773349026</v>
       </c>
       <c r="C26">
-        <v>10.00370848626158</v>
+        <v>9.874820407715085</v>
       </c>
       <c r="D26">
-        <v>13.10786848626158</v>
+        <v>13.10832040771508</v>
       </c>
       <c r="E26">
-        <v>2.67016</v>
+        <v>2.7995</v>
       </c>
       <c r="F26">
-        <v>3.10416</v>
+        <v>3.2335</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>0.707</v>
       </c>
       <c r="M26">
-        <v>0.190285008</v>
+        <v>0.19821355</v>
       </c>
       <c r="N26">
-        <v>0.516714992</v>
+        <v>0.50878645</v>
       </c>
       <c r="O26">
-        <v>0.08267439872000001</v>
+        <v>0.081405832</v>
       </c>
       <c r="P26">
-        <v>0.43404059328</v>
+        <v>0.427380618</v>
       </c>
       <c r="Q26">
-        <v>0.45004059328</v>
+        <v>0.443380618</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09191437115751677</v>
+        <v>0.09245147697798703</v>
       </c>
       <c r="T26">
-        <v>0.6347816766623011</v>
+        <v>0.6421751404503812</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.715479256253336</v>
+        <v>3.566860086003202</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08221160773349026</v>
+        <v>0.08282173338726778</v>
       </c>
       <c r="C27">
-        <v>9.874820407715085</v>
+        <v>9.550664832931753</v>
       </c>
       <c r="D27">
-        <v>13.10832040771508</v>
+        <v>12.91350483293175</v>
       </c>
       <c r="E27">
-        <v>2.7995</v>
+        <v>2.92884</v>
       </c>
       <c r="F27">
-        <v>3.2335</v>
+        <v>3.36284</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3489,45 +3489,45 @@
         <v>0.707</v>
       </c>
       <c r="M27">
-        <v>0.19821355</v>
+        <v>0.215558044</v>
       </c>
       <c r="N27">
-        <v>0.50878645</v>
+        <v>0.491441956</v>
       </c>
       <c r="O27">
-        <v>0.081405832</v>
+        <v>0.07863071296</v>
       </c>
       <c r="P27">
-        <v>0.427380618</v>
+        <v>0.4128112430399999</v>
       </c>
       <c r="Q27">
-        <v>0.443380618</v>
+        <v>0.42881124304</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09245147697798703</v>
+        <v>0.09300309917198349</v>
       </c>
       <c r="T27">
-        <v>0.6421751404503812</v>
+        <v>0.649768427584085</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.16</v>
       </c>
       <c r="W27">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.566860086003202</v>
+        <v>3.279859043441682</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08282173338726778</v>
+        <v>0.0828438590410453</v>
       </c>
       <c r="C28">
-        <v>9.550664832931753</v>
+        <v>9.4143687687762</v>
       </c>
       <c r="D28">
-        <v>12.91350483293175</v>
+        <v>12.9065487687762</v>
       </c>
       <c r="E28">
-        <v>2.92884</v>
+        <v>3.05818</v>
       </c>
       <c r="F28">
-        <v>3.36284</v>
+        <v>3.49218</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3571,28 +3571,28 @@
         <v>0.707</v>
       </c>
       <c r="M28">
-        <v>0.215558044</v>
+        <v>0.223848738</v>
       </c>
       <c r="N28">
-        <v>0.491441956</v>
+        <v>0.483151262</v>
       </c>
       <c r="O28">
-        <v>0.07863071296</v>
+        <v>0.07730420192</v>
       </c>
       <c r="P28">
-        <v>0.4128112430399999</v>
+        <v>0.40584706008</v>
       </c>
       <c r="Q28">
-        <v>0.42881124304</v>
+        <v>0.42184706008</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09300309917198349</v>
+        <v>0.09356983430280177</v>
       </c>
       <c r="T28">
-        <v>0.649768427584085</v>
+        <v>0.6575697499817259</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.279859043441682</v>
+        <v>3.158382782573471</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0828438590410453</v>
+        <v>0.08286598469482281</v>
       </c>
       <c r="C29">
-        <v>9.4143687687762</v>
+        <v>9.278080194574589</v>
       </c>
       <c r="D29">
-        <v>12.9065487687762</v>
+        <v>12.89960019457459</v>
       </c>
       <c r="E29">
-        <v>3.05818</v>
+        <v>3.18752</v>
       </c>
       <c r="F29">
-        <v>3.49218</v>
+        <v>3.62152</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3653,28 +3653,28 @@
         <v>0.707</v>
       </c>
       <c r="M29">
-        <v>0.223848738</v>
+        <v>0.232139432</v>
       </c>
       <c r="N29">
-        <v>0.483151262</v>
+        <v>0.4748605679999999</v>
       </c>
       <c r="O29">
-        <v>0.07730420192</v>
+        <v>0.07597769087999999</v>
       </c>
       <c r="P29">
-        <v>0.40584706008</v>
+        <v>0.3988828771199999</v>
       </c>
       <c r="Q29">
-        <v>0.42184706008</v>
+        <v>0.4148828771199999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09356983430280177</v>
+        <v>0.0941523120761428</v>
       </c>
       <c r="T29">
-        <v>0.6575697499817259</v>
+        <v>0.6655877757793013</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.158382782573471</v>
+        <v>3.045583397481561</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08286598469482281</v>
+        <v>0.08478819034860033</v>
       </c>
       <c r="C30">
-        <v>9.278080194574589</v>
+        <v>8.572354341067182</v>
       </c>
       <c r="D30">
-        <v>12.89960019457459</v>
+        <v>12.32321434106718</v>
       </c>
       <c r="E30">
-        <v>3.18752</v>
+        <v>3.31686</v>
       </c>
       <c r="F30">
-        <v>3.62152</v>
+        <v>3.75086</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3735,45 +3735,45 @@
         <v>0.707</v>
       </c>
       <c r="M30">
-        <v>0.232139432</v>
+        <v>0.269686834</v>
       </c>
       <c r="N30">
-        <v>0.4748605679999999</v>
+        <v>0.4373131659999999</v>
       </c>
       <c r="O30">
-        <v>0.07597769087999999</v>
+        <v>0.06997010655999999</v>
       </c>
       <c r="P30">
-        <v>0.3988828771199999</v>
+        <v>0.3673430594399999</v>
       </c>
       <c r="Q30">
-        <v>0.4148828771199999</v>
+        <v>0.3833430594399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0941523120761428</v>
+        <v>0.09475119767408498</v>
       </c>
       <c r="T30">
-        <v>0.6655877757793013</v>
+        <v>0.6738316614584986</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.16</v>
       </c>
       <c r="W30">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.045583397481561</v>
+        <v>2.621559197064844</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08478819034860033</v>
+        <v>0.08487583600237784</v>
       </c>
       <c r="C31">
-        <v>8.572354341067182</v>
+        <v>8.417958574960998</v>
       </c>
       <c r="D31">
-        <v>12.32321434106718</v>
+        <v>12.298158574961</v>
       </c>
       <c r="E31">
-        <v>3.316859999999999</v>
+        <v>3.446199999999999</v>
       </c>
       <c r="F31">
-        <v>3.750859999999999</v>
+        <v>3.880199999999999</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3817,28 +3817,28 @@
         <v>0.707</v>
       </c>
       <c r="M31">
-        <v>0.269686834</v>
+        <v>0.27898638</v>
       </c>
       <c r="N31">
-        <v>0.437313166</v>
+        <v>0.42801362</v>
       </c>
       <c r="O31">
-        <v>0.06997010655999999</v>
+        <v>0.06848217919999999</v>
       </c>
       <c r="P31">
-        <v>0.36734305944</v>
+        <v>0.3595314408</v>
       </c>
       <c r="Q31">
-        <v>0.38334305944</v>
+        <v>0.3755314408</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09475119767408496</v>
+        <v>0.09536719428911121</v>
       </c>
       <c r="T31">
-        <v>0.6738316614584985</v>
+        <v>0.6823110867285299</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.621559197064844</v>
+        <v>2.534173890496016</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08487583600237784</v>
+        <v>0.08597904165615537</v>
       </c>
       <c r="C32">
-        <v>8.417958574960998</v>
+        <v>7.981733969206966</v>
       </c>
       <c r="D32">
-        <v>12.298158574961</v>
+        <v>11.99127396920696</v>
       </c>
       <c r="E32">
-        <v>3.446199999999999</v>
+        <v>3.575539999999999</v>
       </c>
       <c r="F32">
-        <v>3.880199999999999</v>
+        <v>4.009539999999999</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3899,45 +3899,45 @@
         <v>0.707</v>
       </c>
       <c r="M32">
-        <v>0.27898638</v>
+        <v>0.303923132</v>
       </c>
       <c r="N32">
-        <v>0.42801362</v>
+        <v>0.403076868</v>
       </c>
       <c r="O32">
-        <v>0.06848217919999999</v>
+        <v>0.06449229887999999</v>
       </c>
       <c r="P32">
-        <v>0.3595314408</v>
+        <v>0.33858456912</v>
       </c>
       <c r="Q32">
-        <v>0.3755314408</v>
+        <v>0.35458456912</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09536719428911121</v>
+        <v>0.09600104587848604</v>
       </c>
       <c r="T32">
-        <v>0.6823110867285299</v>
+        <v>0.691036292441171</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.16</v>
       </c>
       <c r="W32">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.534173890496016</v>
+        <v>2.326246098306199</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08597904165615537</v>
+        <v>0.08609944730993288</v>
       </c>
       <c r="C33">
-        <v>7.981733969206966</v>
+        <v>7.819824584519254</v>
       </c>
       <c r="D33">
-        <v>11.99127396920696</v>
+        <v>11.95870458451925</v>
       </c>
       <c r="E33">
-        <v>3.575539999999999</v>
+        <v>3.704879999999999</v>
       </c>
       <c r="F33">
-        <v>4.009539999999999</v>
+        <v>4.138879999999999</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3981,28 +3981,28 @@
         <v>0.707</v>
       </c>
       <c r="M33">
-        <v>0.303923132</v>
+        <v>0.313727104</v>
       </c>
       <c r="N33">
-        <v>0.403076868</v>
+        <v>0.393272896</v>
       </c>
       <c r="O33">
-        <v>0.06449229887999999</v>
+        <v>0.06292366335999999</v>
       </c>
       <c r="P33">
-        <v>0.33858456912</v>
+        <v>0.33034923264</v>
       </c>
       <c r="Q33">
-        <v>0.35458456912</v>
+        <v>0.34634923264</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09600104587848604</v>
+        <v>0.096653540161666</v>
       </c>
       <c r="T33">
-        <v>0.691036292441171</v>
+        <v>0.7000181218512427</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.326246098306199</v>
+        <v>2.253550907734131</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08609944730993288</v>
+        <v>0.08621985296371039</v>
       </c>
       <c r="C34">
-        <v>7.819824584519254</v>
+        <v>7.658091643384192</v>
       </c>
       <c r="D34">
-        <v>11.95870458451925</v>
+        <v>11.92631164338419</v>
       </c>
       <c r="E34">
-        <v>3.704879999999999</v>
+        <v>3.83422</v>
       </c>
       <c r="F34">
-        <v>4.138879999999999</v>
+        <v>4.26822</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4063,28 +4063,28 @@
         <v>0.707</v>
       </c>
       <c r="M34">
-        <v>0.313727104</v>
+        <v>0.323531076</v>
       </c>
       <c r="N34">
-        <v>0.393272896</v>
+        <v>0.3834689239999999</v>
       </c>
       <c r="O34">
-        <v>0.06292366335999999</v>
+        <v>0.06135502783999999</v>
       </c>
       <c r="P34">
-        <v>0.33034923264</v>
+        <v>0.32211389616</v>
       </c>
       <c r="Q34">
-        <v>0.34634923264</v>
+        <v>0.33811389616</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.096653540161666</v>
+        <v>0.09732551188613492</v>
       </c>
       <c r="T34">
-        <v>0.7000181218512427</v>
+        <v>0.7092680655720628</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.253550907734131</v>
+        <v>2.185261486287642</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08621985296371039</v>
+        <v>0.0863402586174879</v>
       </c>
       <c r="C35">
-        <v>7.658091643384192</v>
+        <v>7.496533715859544</v>
       </c>
       <c r="D35">
-        <v>11.92631164338419</v>
+        <v>11.89409371585954</v>
       </c>
       <c r="E35">
-        <v>3.83422</v>
+        <v>3.96356</v>
       </c>
       <c r="F35">
-        <v>4.26822</v>
+        <v>4.39756</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4145,28 +4145,28 @@
         <v>0.707</v>
       </c>
       <c r="M35">
-        <v>0.323531076</v>
+        <v>0.3333350480000001</v>
       </c>
       <c r="N35">
-        <v>0.3834689239999999</v>
+        <v>0.3736649519999999</v>
       </c>
       <c r="O35">
-        <v>0.06135502783999999</v>
+        <v>0.05978639231999999</v>
       </c>
       <c r="P35">
-        <v>0.32211389616</v>
+        <v>0.3138785596799999</v>
       </c>
       <c r="Q35">
-        <v>0.33811389616</v>
+        <v>0.3298785596799999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09732551188613492</v>
+        <v>0.0980178463901332</v>
       </c>
       <c r="T35">
-        <v>0.7092680655720628</v>
+        <v>0.7187983106177562</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.185261486287642</v>
+        <v>2.120989089632122</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0863402586174879</v>
+        <v>0.08646066427126542</v>
       </c>
       <c r="C36">
-        <v>7.496533715859544</v>
+        <v>7.335149387412909</v>
       </c>
       <c r="D36">
-        <v>11.89409371585954</v>
+        <v>11.86204938741291</v>
       </c>
       <c r="E36">
-        <v>3.96356</v>
+        <v>4.0929</v>
       </c>
       <c r="F36">
-        <v>4.39756</v>
+        <v>4.5269</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4227,28 +4227,28 @@
         <v>0.707</v>
       </c>
       <c r="M36">
-        <v>0.3333350480000001</v>
+        <v>0.3431390200000001</v>
       </c>
       <c r="N36">
-        <v>0.3736649519999999</v>
+        <v>0.3638609799999999</v>
       </c>
       <c r="O36">
-        <v>0.05978639231999999</v>
+        <v>0.05821775679999999</v>
       </c>
       <c r="P36">
-        <v>0.3138785596799999</v>
+        <v>0.3056432231999999</v>
       </c>
       <c r="Q36">
-        <v>0.3298785596799999</v>
+        <v>0.3216432231999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0980178463901332</v>
+        <v>0.09873148349425451</v>
       </c>
       <c r="T36">
-        <v>0.7187983106177562</v>
+        <v>0.7286217939725479</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.120989089632122</v>
+        <v>2.060389401356919</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08646066427126542</v>
+        <v>0.08658106992504294</v>
       </c>
       <c r="C37">
-        <v>7.335149387412909</v>
+        <v>7.173937258714723</v>
       </c>
       <c r="D37">
-        <v>11.86204938741291</v>
+        <v>11.83017725871472</v>
       </c>
       <c r="E37">
-        <v>4.0929</v>
+        <v>4.22224</v>
       </c>
       <c r="F37">
-        <v>4.5269</v>
+        <v>4.65624</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4309,28 +4309,28 @@
         <v>0.707</v>
       </c>
       <c r="M37">
-        <v>0.3431390200000001</v>
+        <v>0.3529429920000001</v>
       </c>
       <c r="N37">
-        <v>0.3638609799999999</v>
+        <v>0.3540570079999999</v>
       </c>
       <c r="O37">
-        <v>0.05821775679999999</v>
+        <v>0.05664912127999999</v>
       </c>
       <c r="P37">
-        <v>0.3056432231999999</v>
+        <v>0.2974078867199999</v>
       </c>
       <c r="Q37">
-        <v>0.3216432231999999</v>
+        <v>0.3134078867199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09873148349425451</v>
+        <v>0.09946742175787961</v>
       </c>
       <c r="T37">
-        <v>0.7286217939725479</v>
+        <v>0.7387522611821769</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.060389401356919</v>
+        <v>2.003156362430338</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08658106992504294</v>
+        <v>0.09111483557882046</v>
       </c>
       <c r="C38">
-        <v>7.173937258714724</v>
+        <v>5.957672881708962</v>
       </c>
       <c r="D38">
-        <v>11.83017725871472</v>
+        <v>10.74325288170896</v>
       </c>
       <c r="E38">
-        <v>4.222239999999999</v>
+        <v>4.351579999999999</v>
       </c>
       <c r="F38">
-        <v>4.656239999999999</v>
+        <v>4.78558</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4391,45 +4391,45 @@
         <v>0.707</v>
       </c>
       <c r="M38">
-        <v>0.352942992</v>
+        <v>0.4307021999999999</v>
       </c>
       <c r="N38">
-        <v>0.354057008</v>
+        <v>0.2762978</v>
       </c>
       <c r="O38">
-        <v>0.05664912127999999</v>
+        <v>0.04420764800000001</v>
       </c>
       <c r="P38">
-        <v>0.29740788672</v>
+        <v>0.232090152</v>
       </c>
       <c r="Q38">
-        <v>0.31340788672</v>
+        <v>0.248090152</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09946742175787959</v>
+        <v>0.1002267231409849</v>
       </c>
       <c r="T38">
-        <v>0.7387522611821767</v>
+        <v>0.7492043305254447</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.16</v>
       </c>
       <c r="W38">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.003156362430338</v>
+        <v>1.641505429969942</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09111483557882046</v>
+        <v>0.09135452123259798</v>
       </c>
       <c r="C39">
-        <v>5.957672881708962</v>
+        <v>5.776402385216307</v>
       </c>
       <c r="D39">
-        <v>10.74325288170896</v>
+        <v>10.69132238521631</v>
       </c>
       <c r="E39">
-        <v>4.351579999999999</v>
+        <v>4.480919999999999</v>
       </c>
       <c r="F39">
-        <v>4.78558</v>
+        <v>4.91492</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4473,28 +4473,28 @@
         <v>0.707</v>
       </c>
       <c r="M39">
-        <v>0.4307021999999999</v>
+        <v>0.4423427999999999</v>
       </c>
       <c r="N39">
-        <v>0.2762978</v>
+        <v>0.2646572</v>
       </c>
       <c r="O39">
-        <v>0.04420764800000001</v>
+        <v>0.042345152</v>
       </c>
       <c r="P39">
-        <v>0.232090152</v>
+        <v>0.222312048</v>
       </c>
       <c r="Q39">
-        <v>0.248090152</v>
+        <v>0.2383120480000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1002267231409849</v>
+        <v>0.1010105181170935</v>
       </c>
       <c r="T39">
-        <v>0.7492043305254447</v>
+        <v>0.7599935633959147</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.641505429969942</v>
+        <v>1.598307918654944</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09135452123259798</v>
+        <v>0.09159420688637548</v>
       </c>
       <c r="C40">
-        <v>5.776402385216307</v>
+        <v>5.595631514597802</v>
       </c>
       <c r="D40">
-        <v>10.69132238521631</v>
+        <v>10.6398915145978</v>
       </c>
       <c r="E40">
-        <v>4.480919999999999</v>
+        <v>4.610259999999999</v>
       </c>
       <c r="F40">
-        <v>4.91492</v>
+        <v>5.04426</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4555,28 +4555,28 @@
         <v>0.707</v>
       </c>
       <c r="M40">
-        <v>0.4423427999999999</v>
+        <v>0.4539833999999999</v>
       </c>
       <c r="N40">
-        <v>0.2646572</v>
+        <v>0.2530166</v>
       </c>
       <c r="O40">
-        <v>0.042345152</v>
+        <v>0.04048265600000001</v>
       </c>
       <c r="P40">
-        <v>0.222312048</v>
+        <v>0.212533944</v>
       </c>
       <c r="Q40">
-        <v>0.2383120480000001</v>
+        <v>0.228533944</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1010105181170935</v>
+        <v>0.1018200112891401</v>
       </c>
       <c r="T40">
-        <v>0.7599935633959147</v>
+        <v>0.7711365416064002</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.598307918654944</v>
+        <v>1.557325664330458</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09159420688637548</v>
+        <v>0.09183389254015302</v>
       </c>
       <c r="C41">
-        <v>5.595631514597802</v>
+        <v>5.41535309398528</v>
       </c>
       <c r="D41">
-        <v>10.6398915145978</v>
+        <v>10.58895309398528</v>
       </c>
       <c r="E41">
-        <v>4.610259999999999</v>
+        <v>4.7396</v>
       </c>
       <c r="F41">
-        <v>5.04426</v>
+        <v>5.1736</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4637,28 +4637,28 @@
         <v>0.707</v>
       </c>
       <c r="M41">
-        <v>0.4539833999999999</v>
+        <v>0.465624</v>
       </c>
       <c r="N41">
-        <v>0.2530166</v>
+        <v>0.2413759999999999</v>
       </c>
       <c r="O41">
-        <v>0.04048265600000001</v>
+        <v>0.03862015999999999</v>
       </c>
       <c r="P41">
-        <v>0.212533944</v>
+        <v>0.2027558399999999</v>
       </c>
       <c r="Q41">
-        <v>0.228533944</v>
+        <v>0.2187558399999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1018200112891401</v>
+        <v>0.1026564875669217</v>
       </c>
       <c r="T41">
-        <v>0.7711365416064002</v>
+        <v>0.782650952423902</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.557325664330458</v>
+        <v>1.518392522722196</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09183389254015302</v>
+        <v>0.112739145061865</v>
       </c>
       <c r="C42">
-        <v>5.41535309398528</v>
+        <v>2.16689072577292</v>
       </c>
       <c r="D42">
-        <v>10.58895309398528</v>
+        <v>7.469830725772921</v>
       </c>
       <c r="E42">
-        <v>4.7396</v>
+        <v>4.86894</v>
       </c>
       <c r="F42">
-        <v>5.1736</v>
+        <v>5.30294</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4719,45 +4719,45 @@
         <v>0.707</v>
       </c>
       <c r="M42">
-        <v>0.465624</v>
+        <v>0.7784715920000002</v>
       </c>
       <c r="N42">
-        <v>0.2413759999999999</v>
+        <v>-0.07147159200000019</v>
       </c>
       <c r="O42">
-        <v>0.03862015999999999</v>
+        <v>-0.01143545472000003</v>
       </c>
       <c r="P42">
-        <v>0.2027558399999999</v>
+        <v>-0.06003613728000017</v>
       </c>
       <c r="Q42">
-        <v>0.2187558399999999</v>
+        <v>-0.04403613728000016</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1026564875669217</v>
+        <v>0.103893366089398</v>
       </c>
       <c r="T42">
-        <v>0.782650952423902</v>
+        <v>0.7996770508530271</v>
       </c>
       <c r="U42">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.16</v>
+        <v>0.1453103763354797</v>
       </c>
       <c r="W42">
-        <v>0.0756</v>
+        <v>0.1254684367539516</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.518392522722196</v>
+        <v>0.9081898520967479</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.112739145061865</v>
+        <v>0.113749145061865</v>
       </c>
       <c r="C43">
-        <v>2.16689072577292</v>
+        <v>1.932736776512568</v>
       </c>
       <c r="D43">
-        <v>7.469830725772921</v>
+        <v>7.365016776512569</v>
       </c>
       <c r="E43">
-        <v>4.86894</v>
+        <v>4.99828</v>
       </c>
       <c r="F43">
-        <v>5.30294</v>
+        <v>5.43228</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4801,37 +4801,37 @@
         <v>0.707</v>
       </c>
       <c r="M43">
-        <v>0.7784715920000002</v>
+        <v>0.7974587040000002</v>
       </c>
       <c r="N43">
-        <v>-0.07147159200000019</v>
+        <v>-0.09045870400000022</v>
       </c>
       <c r="O43">
-        <v>-0.01143545472000003</v>
+        <v>-0.01447339264000004</v>
       </c>
       <c r="P43">
-        <v>-0.06003613728000017</v>
+        <v>-0.07598531136000018</v>
       </c>
       <c r="Q43">
-        <v>-0.04403613728000016</v>
+        <v>-0.05998531136000018</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.103893366089398</v>
+        <v>0.10489497584956</v>
       </c>
       <c r="T43">
-        <v>0.7996770508530271</v>
+        <v>0.8134645862125621</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1453103763354797</v>
+        <v>0.1418506054703492</v>
       </c>
       <c r="W43">
-        <v>0.1254684367539516</v>
+        <v>0.1259763311169527</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.9081898520967479</v>
+        <v>0.8865662841896824</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.113749145061865</v>
+        <v>0.114759145061865</v>
       </c>
       <c r="C44">
-        <v>1.932736776512569</v>
+        <v>1.701483547861796</v>
       </c>
       <c r="D44">
-        <v>7.365016776512569</v>
+        <v>7.263103547861796</v>
       </c>
       <c r="E44">
-        <v>4.998279999999999</v>
+        <v>5.127619999999999</v>
       </c>
       <c r="F44">
-        <v>5.43228</v>
+        <v>5.56162</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4883,37 +4883,37 @@
         <v>0.707</v>
       </c>
       <c r="M44">
-        <v>0.797458704</v>
+        <v>0.816445816</v>
       </c>
       <c r="N44">
-        <v>-0.090458704</v>
+        <v>-0.109445816</v>
       </c>
       <c r="O44">
-        <v>-0.01447339264</v>
+        <v>-0.01751133056000001</v>
       </c>
       <c r="P44">
-        <v>-0.07598531136</v>
+        <v>-0.09193448544000002</v>
       </c>
       <c r="Q44">
-        <v>-0.05998531136</v>
+        <v>-0.07593448544000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.10489497584956</v>
+        <v>0.105931729811833</v>
       </c>
       <c r="T44">
-        <v>0.813464586212562</v>
+        <v>0.8277358947426069</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1418506054703492</v>
+        <v>0.1385517541803411</v>
       </c>
       <c r="W44">
-        <v>0.1259763311169527</v>
+        <v>0.1264606024863259</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8865662841896826</v>
+        <v>0.8659484636271318</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.114759145061865</v>
+        <v>0.115769145061865</v>
       </c>
       <c r="C45">
-        <v>1.701483547861796</v>
+        <v>1.47301226739236</v>
       </c>
       <c r="D45">
-        <v>7.263103547861796</v>
+        <v>7.16397226739236</v>
       </c>
       <c r="E45">
-        <v>5.127619999999999</v>
+        <v>5.256959999999999</v>
       </c>
       <c r="F45">
-        <v>5.56162</v>
+        <v>5.69096</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4965,37 +4965,37 @@
         <v>0.707</v>
       </c>
       <c r="M45">
-        <v>0.816445816</v>
+        <v>0.835432928</v>
       </c>
       <c r="N45">
-        <v>-0.109445816</v>
+        <v>-0.1284329280000001</v>
       </c>
       <c r="O45">
-        <v>-0.01751133056000001</v>
+        <v>-0.02054926848000001</v>
       </c>
       <c r="P45">
-        <v>-0.09193448544000002</v>
+        <v>-0.10788365952</v>
       </c>
       <c r="Q45">
-        <v>-0.07593448544000002</v>
+        <v>-0.09188365952000005</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.105931729811833</v>
+        <v>0.10700551070133</v>
       </c>
       <c r="T45">
-        <v>0.8277358947426069</v>
+        <v>0.8425168928630106</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1385517541803411</v>
+        <v>0.1354028506762424</v>
       </c>
       <c r="W45">
-        <v>0.1264606024863259</v>
+        <v>0.1269228615207276</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8659484636271318</v>
+        <v>0.8462678167265152</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.115769145061865</v>
+        <v>0.1167791450618649</v>
       </c>
       <c r="C46">
-        <v>1.47301226739236</v>
+        <v>1.247210559680834</v>
       </c>
       <c r="D46">
-        <v>7.16397226739236</v>
+        <v>7.067510559680834</v>
       </c>
       <c r="E46">
-        <v>5.256959999999999</v>
+        <v>5.386299999999999</v>
       </c>
       <c r="F46">
-        <v>5.69096</v>
+        <v>5.8203</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5047,37 +5047,37 @@
         <v>0.707</v>
       </c>
       <c r="M46">
-        <v>0.835432928</v>
+        <v>0.85442004</v>
       </c>
       <c r="N46">
-        <v>-0.1284329280000001</v>
+        <v>-0.1474200400000001</v>
       </c>
       <c r="O46">
-        <v>-0.02054926848000001</v>
+        <v>-0.02358720640000002</v>
       </c>
       <c r="P46">
-        <v>-0.10788365952</v>
+        <v>-0.1238328336000001</v>
       </c>
       <c r="Q46">
-        <v>-0.09188365952000005</v>
+        <v>-0.1078328336000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.10700551070133</v>
+        <v>0.1081183381686269</v>
       </c>
       <c r="T46">
-        <v>0.8425168928630106</v>
+        <v>0.8578353818241562</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1354028506762424</v>
+        <v>0.1323938984389926</v>
       </c>
       <c r="W46">
-        <v>0.1269228615207276</v>
+        <v>0.1273645757091559</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8462678167265152</v>
+        <v>0.8274618652437037</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1167791450618649</v>
+        <v>0.117789145061865</v>
       </c>
       <c r="C47">
-        <v>1.247210559680834</v>
+        <v>1.023972021357392</v>
       </c>
       <c r="D47">
-        <v>7.067510559680834</v>
+        <v>6.973612021357392</v>
       </c>
       <c r="E47">
-        <v>5.386299999999999</v>
+        <v>5.515639999999999</v>
       </c>
       <c r="F47">
-        <v>5.8203</v>
+        <v>5.94964</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5129,37 +5129,37 @@
         <v>0.707</v>
       </c>
       <c r="M47">
-        <v>0.85442004</v>
+        <v>0.8734071520000001</v>
       </c>
       <c r="N47">
-        <v>-0.1474200400000001</v>
+        <v>-0.1664071520000001</v>
       </c>
       <c r="O47">
-        <v>-0.02358720640000002</v>
+        <v>-0.02662514432000002</v>
       </c>
       <c r="P47">
-        <v>-0.1238328336000001</v>
+        <v>-0.1397820076800001</v>
       </c>
       <c r="Q47">
-        <v>-0.1078328336000001</v>
+        <v>-0.1237820076800001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1081183381686269</v>
+        <v>0.1092723814680459</v>
       </c>
       <c r="T47">
-        <v>0.8578353818241562</v>
+        <v>0.8737212222283073</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1323938984389926</v>
+        <v>0.129515770212058</v>
       </c>
       <c r="W47">
-        <v>0.1273645757091559</v>
+        <v>0.1277870849328699</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8274618652437037</v>
+        <v>0.8094735638253623</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.117789145061865</v>
+        <v>0.1447630820210314</v>
       </c>
       <c r="C48">
-        <v>1.023972021357392</v>
+        <v>-0.9317415621518483</v>
       </c>
       <c r="D48">
-        <v>6.973612021357392</v>
+        <v>5.147238437848151</v>
       </c>
       <c r="E48">
-        <v>5.515639999999999</v>
+        <v>5.644979999999999</v>
       </c>
       <c r="F48">
-        <v>5.94964</v>
+        <v>6.07898</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5211,45 +5211,45 @@
         <v>0.707</v>
       </c>
       <c r="M48">
-        <v>0.8734071520000001</v>
+        <v>1.220659184</v>
       </c>
       <c r="N48">
-        <v>-0.1664071520000001</v>
+        <v>-0.5136591840000001</v>
       </c>
       <c r="O48">
-        <v>-0.02662514432000002</v>
+        <v>-0.08218546944000002</v>
       </c>
       <c r="P48">
-        <v>-0.1397820076800001</v>
+        <v>-0.4314737145600001</v>
       </c>
       <c r="Q48">
-        <v>-0.1237820076800001</v>
+        <v>-0.41547371456</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1092723814680459</v>
+        <v>0.1115717414187004</v>
       </c>
       <c r="T48">
-        <v>0.8737212222283073</v>
+        <v>0.9053727774396081</v>
       </c>
       <c r="U48">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.129515770212058</v>
+        <v>0.09267123983724516</v>
       </c>
       <c r="W48">
-        <v>0.1277870849328699</v>
+        <v>0.1821916150406812</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8094735638253623</v>
+        <v>0.5791952489827823</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1447630820210314</v>
+        <v>0.1463130820210314</v>
       </c>
       <c r="C49">
-        <v>-0.9317415621518483</v>
+        <v>-1.137395928589966</v>
       </c>
       <c r="D49">
-        <v>5.147238437848151</v>
+        <v>5.070924071410035</v>
       </c>
       <c r="E49">
-        <v>5.644979999999999</v>
+        <v>5.77432</v>
       </c>
       <c r="F49">
-        <v>6.07898</v>
+        <v>6.208320000000001</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5293,37 +5293,37 @@
         <v>0.707</v>
       </c>
       <c r="M49">
-        <v>1.220659184</v>
+        <v>1.246630656</v>
       </c>
       <c r="N49">
-        <v>-0.5136591840000001</v>
+        <v>-0.5396306560000003</v>
       </c>
       <c r="O49">
-        <v>-0.08218546944000002</v>
+        <v>-0.08634090496000005</v>
       </c>
       <c r="P49">
-        <v>-0.4314737145600001</v>
+        <v>-0.4532897510400002</v>
       </c>
       <c r="Q49">
-        <v>-0.41547371456</v>
+        <v>-0.4372897510400002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1115717414187004</v>
+        <v>0.1128365825998292</v>
       </c>
       <c r="T49">
-        <v>0.9053727774396081</v>
+        <v>0.9227837923903697</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.09267123983724516</v>
+        <v>0.09074058900730256</v>
       </c>
       <c r="W49">
-        <v>0.1821916150406812</v>
+        <v>0.1825792897273337</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5791952489827823</v>
+        <v>0.567128681295641</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1463130820210313</v>
+        <v>0.1478630820210313</v>
       </c>
       <c r="C50">
-        <v>-1.137395928589963</v>
+        <v>-1.340820440083349</v>
       </c>
       <c r="D50">
-        <v>5.070924071410037</v>
+        <v>4.99683955991665</v>
       </c>
       <c r="E50">
-        <v>5.774319999999999</v>
+        <v>5.903659999999999</v>
       </c>
       <c r="F50">
-        <v>6.20832</v>
+        <v>6.33766</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5375,37 +5375,37 @@
         <v>0.707</v>
       </c>
       <c r="M50">
-        <v>1.246630656</v>
+        <v>1.272602128</v>
       </c>
       <c r="N50">
-        <v>-0.539630656</v>
+        <v>-0.565602128</v>
       </c>
       <c r="O50">
-        <v>-0.08634090496000001</v>
+        <v>-0.09049634047999999</v>
       </c>
       <c r="P50">
-        <v>-0.45328975104</v>
+        <v>-0.47510578752</v>
       </c>
       <c r="Q50">
-        <v>-0.43728975104</v>
+        <v>-0.45910578752</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1128365825998292</v>
+        <v>0.1141510253959043</v>
       </c>
       <c r="T50">
-        <v>0.9227837923903697</v>
+        <v>0.9408775922411611</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.09074058900730257</v>
+        <v>0.0888887402520515</v>
       </c>
       <c r="W50">
-        <v>0.1825792897273337</v>
+        <v>0.1829511409573881</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5671286812956411</v>
+        <v>0.555554626575322</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1478630820210313</v>
+        <v>0.1494130820210313</v>
       </c>
       <c r="C51">
-        <v>-1.340820440083349</v>
+        <v>-1.542111421669146</v>
       </c>
       <c r="D51">
-        <v>4.99683955991665</v>
+        <v>4.924888578330854</v>
       </c>
       <c r="E51">
-        <v>5.903659999999999</v>
+        <v>6.032999999999999</v>
       </c>
       <c r="F51">
-        <v>6.33766</v>
+        <v>6.467</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5457,37 +5457,37 @@
         <v>0.707</v>
       </c>
       <c r="M51">
-        <v>1.272602128</v>
+        <v>1.2985736</v>
       </c>
       <c r="N51">
-        <v>-0.565602128</v>
+        <v>-0.5915735999999999</v>
       </c>
       <c r="O51">
-        <v>-0.09049634047999999</v>
+        <v>-0.09465177599999999</v>
       </c>
       <c r="P51">
-        <v>-0.47510578752</v>
+        <v>-0.496921824</v>
       </c>
       <c r="Q51">
-        <v>-0.45910578752</v>
+        <v>-0.4809218239999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1141510253959043</v>
+        <v>0.1155180459038224</v>
       </c>
       <c r="T51">
-        <v>0.9408775922411611</v>
+        <v>0.9596951440859844</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.0888887402520515</v>
+        <v>0.08711096544701048</v>
       </c>
       <c r="W51">
-        <v>0.1829511409573881</v>
+        <v>0.1833081181382403</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.555554626575322</v>
+        <v>0.5444435340438154</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1494130820210313</v>
+        <v>0.1509630820210313</v>
       </c>
       <c r="C52">
-        <v>-1.542111421669146</v>
+        <v>-1.741359729086906</v>
       </c>
       <c r="D52">
-        <v>4.924888578330854</v>
+        <v>4.854980270913094</v>
       </c>
       <c r="E52">
-        <v>6.032999999999999</v>
+        <v>6.162339999999999</v>
       </c>
       <c r="F52">
-        <v>6.467</v>
+        <v>6.59634</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5539,37 +5539,37 @@
         <v>0.707</v>
       </c>
       <c r="M52">
-        <v>1.2985736</v>
+        <v>1.324545072</v>
       </c>
       <c r="N52">
-        <v>-0.5915735999999999</v>
+        <v>-0.6175450720000001</v>
       </c>
       <c r="O52">
-        <v>-0.09465177599999999</v>
+        <v>-0.09880721152000002</v>
       </c>
       <c r="P52">
-        <v>-0.496921824</v>
+        <v>-0.51873786048</v>
       </c>
       <c r="Q52">
-        <v>-0.4809218239999999</v>
+        <v>-0.50273786048</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1155180459038224</v>
+        <v>0.1169408631671657</v>
       </c>
       <c r="T52">
-        <v>0.9596951440859844</v>
+        <v>0.9792807592714127</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.08711096544701048</v>
+        <v>0.08540290730099065</v>
       </c>
       <c r="W52">
-        <v>0.1833081181382403</v>
+        <v>0.1836510962139611</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5444435340438154</v>
+        <v>0.5337681706311916</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1509630820210313</v>
+        <v>0.1525130820210313</v>
       </c>
       <c r="C53">
-        <v>-1.741359729086906</v>
+        <v>-1.938651131526222</v>
       </c>
       <c r="D53">
-        <v>4.854980270913094</v>
+        <v>4.787028868473778</v>
       </c>
       <c r="E53">
-        <v>6.162339999999999</v>
+        <v>6.291679999999999</v>
       </c>
       <c r="F53">
-        <v>6.59634</v>
+        <v>6.72568</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5621,37 +5621,37 @@
         <v>0.707</v>
       </c>
       <c r="M53">
-        <v>1.324545072</v>
+        <v>1.350516544</v>
       </c>
       <c r="N53">
-        <v>-0.6175450720000001</v>
+        <v>-0.643516544</v>
       </c>
       <c r="O53">
-        <v>-0.09880721152000002</v>
+        <v>-0.10296264704</v>
       </c>
       <c r="P53">
-        <v>-0.51873786048</v>
+        <v>-0.54055389696</v>
       </c>
       <c r="Q53">
-        <v>-0.50273786048</v>
+        <v>-0.52455389696</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1169408631671657</v>
+        <v>0.1184229644831483</v>
       </c>
       <c r="T53">
-        <v>0.9792807592714127</v>
+        <v>0.9996824417562339</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.08540290730099065</v>
+        <v>0.08376054369904853</v>
       </c>
       <c r="W53">
-        <v>0.1836510962139611</v>
+        <v>0.1839808828252311</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5337681706311916</v>
+        <v>0.5235033981190533</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1525130820210313</v>
+        <v>0.1540630820210313</v>
       </c>
       <c r="C54">
-        <v>-1.938651131526222</v>
+        <v>-2.134066662675889</v>
       </c>
       <c r="D54">
-        <v>4.787028868473778</v>
+        <v>4.720953337324111</v>
       </c>
       <c r="E54">
-        <v>6.291679999999999</v>
+        <v>6.42102</v>
       </c>
       <c r="F54">
-        <v>6.72568</v>
+        <v>6.85502</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5703,37 +5703,37 @@
         <v>0.707</v>
       </c>
       <c r="M54">
-        <v>1.350516544</v>
+        <v>1.376488016</v>
       </c>
       <c r="N54">
-        <v>-0.643516544</v>
+        <v>-0.669488016</v>
       </c>
       <c r="O54">
-        <v>-0.10296264704</v>
+        <v>-0.10711808256</v>
       </c>
       <c r="P54">
-        <v>-0.54055389696</v>
+        <v>-0.56236993344</v>
       </c>
       <c r="Q54">
-        <v>-0.52455389696</v>
+        <v>-0.54636993344</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1184229644831483</v>
+        <v>0.1199681339402365</v>
       </c>
       <c r="T54">
-        <v>0.9996824417562339</v>
+        <v>1.020952280942536</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.08376054369904853</v>
+        <v>0.08218015608208536</v>
       </c>
       <c r="W54">
-        <v>0.1839808828252311</v>
+        <v>0.1842982246587173</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5235033981190533</v>
+        <v>0.5136259755130335</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1540630820210313</v>
+        <v>0.1556130820210313</v>
       </c>
       <c r="C55">
-        <v>-2.134066662675889</v>
+        <v>-2.327682943095635</v>
       </c>
       <c r="D55">
-        <v>4.720953337324111</v>
+        <v>4.656677056904365</v>
       </c>
       <c r="E55">
-        <v>6.42102</v>
+        <v>6.55036</v>
       </c>
       <c r="F55">
-        <v>6.85502</v>
+        <v>6.98436</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5785,37 +5785,37 @@
         <v>0.707</v>
       </c>
       <c r="M55">
-        <v>1.376488016</v>
+        <v>1.402459488</v>
       </c>
       <c r="N55">
-        <v>-0.669488016</v>
+        <v>-0.6954594880000001</v>
       </c>
       <c r="O55">
-        <v>-0.10711808256</v>
+        <v>-0.11127351808</v>
       </c>
       <c r="P55">
-        <v>-0.56236993344</v>
+        <v>-0.58418596992</v>
       </c>
       <c r="Q55">
-        <v>-0.54636993344</v>
+        <v>-0.56818596992</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1199681339402365</v>
+        <v>0.1215804846780678</v>
       </c>
       <c r="T55">
-        <v>1.020952280942536</v>
+        <v>1.043146895745635</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.08218015608208536</v>
+        <v>0.0806583013398245</v>
       </c>
       <c r="W55">
-        <v>0.1842982246587173</v>
+        <v>0.1846038130909632</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5136259755130335</v>
+        <v>0.5041143833739031</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1556130820210313</v>
+        <v>0.1766487076372313</v>
       </c>
       <c r="C56">
-        <v>-2.327682943095635</v>
+        <v>-3.183270626936755</v>
       </c>
       <c r="D56">
-        <v>4.656677056904365</v>
+        <v>3.930429373063246</v>
       </c>
       <c r="E56">
-        <v>6.55036</v>
+        <v>6.6797</v>
       </c>
       <c r="F56">
-        <v>6.98436</v>
+        <v>7.113700000000001</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5867,45 +5867,45 @@
         <v>0.707</v>
       </c>
       <c r="M56">
-        <v>1.402459488</v>
+        <v>1.67741046</v>
       </c>
       <c r="N56">
-        <v>-0.6954594880000001</v>
+        <v>-0.9704104600000002</v>
       </c>
       <c r="O56">
-        <v>-0.11127351808</v>
+        <v>-0.1552656736</v>
       </c>
       <c r="P56">
-        <v>-0.58418596992</v>
+        <v>-0.8151447864000001</v>
       </c>
       <c r="Q56">
-        <v>-0.56818596992</v>
+        <v>-0.7991447864000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1215804846780678</v>
+        <v>0.1237881079291358</v>
       </c>
       <c r="T56">
-        <v>1.043146895745635</v>
+        <v>1.073535660756978</v>
       </c>
       <c r="U56">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0806583013398245</v>
+        <v>0.06743728067607256</v>
       </c>
       <c r="W56">
-        <v>0.1846038130909632</v>
+        <v>0.2198982892165821</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.5041143833739031</v>
+        <v>0.4214830042254535</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1766487076372313</v>
+        <v>0.1785487076372313</v>
       </c>
       <c r="C57">
-        <v>-3.183270626936755</v>
+        <v>-3.367208000604612</v>
       </c>
       <c r="D57">
-        <v>3.930429373063246</v>
+        <v>3.875831999395388</v>
       </c>
       <c r="E57">
-        <v>6.6797</v>
+        <v>6.80904</v>
       </c>
       <c r="F57">
-        <v>7.113700000000001</v>
+        <v>7.243040000000001</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5949,37 +5949,37 @@
         <v>0.707</v>
       </c>
       <c r="M57">
-        <v>1.67741046</v>
+        <v>1.707908832</v>
       </c>
       <c r="N57">
-        <v>-0.9704104600000002</v>
+        <v>-1.000908832</v>
       </c>
       <c r="O57">
-        <v>-0.1552656736</v>
+        <v>-0.1601454131200001</v>
       </c>
       <c r="P57">
-        <v>-0.8151447864000001</v>
+        <v>-0.8407634188800003</v>
       </c>
       <c r="Q57">
-        <v>-0.7991447864000001</v>
+        <v>-0.8247634188800003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1237881079291358</v>
+        <v>0.1255605649275252</v>
       </c>
       <c r="T57">
-        <v>1.073535660756978</v>
+        <v>1.097934198501455</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06743728067607256</v>
+        <v>0.06623304352114269</v>
       </c>
       <c r="W57">
-        <v>0.2198982892165821</v>
+        <v>0.2201822483377146</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4214830042254535</v>
+        <v>0.4139565220071417</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1785487076372313</v>
+        <v>0.1804487076372313</v>
       </c>
       <c r="C58">
-        <v>-3.367208000604612</v>
+        <v>-3.549649337532503</v>
       </c>
       <c r="D58">
-        <v>3.875831999395388</v>
+        <v>3.822730662467497</v>
       </c>
       <c r="E58">
-        <v>6.80904</v>
+        <v>6.93838</v>
       </c>
       <c r="F58">
-        <v>7.243040000000001</v>
+        <v>7.372380000000001</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6031,37 +6031,37 @@
         <v>0.707</v>
       </c>
       <c r="M58">
-        <v>1.707908832</v>
+        <v>1.738407204</v>
       </c>
       <c r="N58">
-        <v>-1.000908832</v>
+        <v>-1.031407204</v>
       </c>
       <c r="O58">
-        <v>-0.1601454131200001</v>
+        <v>-0.16502515264</v>
       </c>
       <c r="P58">
-        <v>-0.8407634188800003</v>
+        <v>-0.8663820513600001</v>
       </c>
       <c r="Q58">
-        <v>-0.8247634188800003</v>
+        <v>-0.8503820513600001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1255605649275252</v>
+        <v>0.1274154617863049</v>
       </c>
       <c r="T58">
-        <v>1.097934198501455</v>
+        <v>1.123467551954977</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06623304352114269</v>
+        <v>0.06507106030147351</v>
       </c>
       <c r="W58">
-        <v>0.2201822483377146</v>
+        <v>0.2204562439809126</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4139565220071417</v>
+        <v>0.4066941268842096</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1804487076372313</v>
+        <v>0.1823487076372313</v>
       </c>
       <c r="C59">
-        <v>-3.549649337532503</v>
+        <v>-3.73065529658953</v>
       </c>
       <c r="D59">
-        <v>3.822730662467497</v>
+        <v>3.77106470341047</v>
       </c>
       <c r="E59">
-        <v>6.93838</v>
+        <v>7.06772</v>
       </c>
       <c r="F59">
-        <v>7.372380000000001</v>
+        <v>7.501720000000001</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6113,37 +6113,37 @@
         <v>0.707</v>
       </c>
       <c r="M59">
-        <v>1.738407204</v>
+        <v>1.768905576</v>
       </c>
       <c r="N59">
-        <v>-1.031407204</v>
+        <v>-1.061905576</v>
       </c>
       <c r="O59">
-        <v>-0.16502515264</v>
+        <v>-0.1699048921600001</v>
       </c>
       <c r="P59">
-        <v>-0.8663820513600001</v>
+        <v>-0.8920006838400004</v>
       </c>
       <c r="Q59">
-        <v>-0.8503820513600001</v>
+        <v>-0.8760006838400004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1274154617863049</v>
+        <v>0.1293586870669312</v>
       </c>
       <c r="T59">
-        <v>1.123467551954977</v>
+        <v>1.150216779382477</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06507106030147351</v>
+        <v>0.06394914546868949</v>
       </c>
       <c r="W59">
-        <v>0.2204562439809126</v>
+        <v>0.220720791498483</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4066941268842096</v>
+        <v>0.3996821591793093</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1823487076372312</v>
+        <v>0.1842487076372312</v>
       </c>
       <c r="C60">
-        <v>-3.730655296589527</v>
+        <v>-3.910283301045597</v>
       </c>
       <c r="D60">
-        <v>3.771064703410472</v>
+        <v>3.720776698954402</v>
       </c>
       <c r="E60">
-        <v>7.067719999999999</v>
+        <v>7.197059999999999</v>
       </c>
       <c r="F60">
-        <v>7.501719999999999</v>
+        <v>7.631059999999999</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6195,37 +6195,37 @@
         <v>0.707</v>
       </c>
       <c r="M60">
-        <v>1.768905576</v>
+        <v>1.799403948</v>
       </c>
       <c r="N60">
-        <v>-1.061905576</v>
+        <v>-1.092403948</v>
       </c>
       <c r="O60">
-        <v>-0.16990489216</v>
+        <v>-0.17478463168</v>
       </c>
       <c r="P60">
-        <v>-0.89200068384</v>
+        <v>-0.9176193163199999</v>
       </c>
       <c r="Q60">
-        <v>-0.87600068384</v>
+        <v>-0.9016193163199999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1293586870669312</v>
+        <v>0.1313967038246612</v>
       </c>
       <c r="T60">
-        <v>1.150216779382476</v>
+        <v>1.178270847172293</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06394914546868952</v>
+        <v>0.0628652616471863</v>
       </c>
       <c r="W60">
-        <v>0.220720791498483</v>
+        <v>0.2209763713035935</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3996821591793094</v>
+        <v>0.3929078852949143</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1842487076372312</v>
+        <v>0.1861487076372312</v>
       </c>
       <c r="C61">
-        <v>-3.910283301045597</v>
+        <v>-4.088587751469625</v>
       </c>
       <c r="D61">
-        <v>3.720776698954402</v>
+        <v>3.671812248530374</v>
       </c>
       <c r="E61">
-        <v>7.197059999999999</v>
+        <v>7.326399999999999</v>
       </c>
       <c r="F61">
-        <v>7.631059999999999</v>
+        <v>7.760399999999999</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6277,37 +6277,37 @@
         <v>0.707</v>
       </c>
       <c r="M61">
-        <v>1.799403948</v>
+        <v>1.82990232</v>
       </c>
       <c r="N61">
-        <v>-1.092403948</v>
+        <v>-1.12290232</v>
       </c>
       <c r="O61">
-        <v>-0.17478463168</v>
+        <v>-0.1796643712</v>
       </c>
       <c r="P61">
-        <v>-0.9176193163199999</v>
+        <v>-0.9432379487999998</v>
       </c>
       <c r="Q61">
-        <v>-0.9016193163199999</v>
+        <v>-0.9272379487999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1313967038246612</v>
+        <v>0.1335366214202777</v>
       </c>
       <c r="T61">
-        <v>1.178270847172293</v>
+        <v>1.2077276183516</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0628652616471863</v>
+        <v>0.06181750728639986</v>
       </c>
       <c r="W61">
-        <v>0.2209763713035935</v>
+        <v>0.2212234317818669</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3929078852949143</v>
+        <v>0.3863594205399992</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1861487076372312</v>
+        <v>0.1880487076372312</v>
       </c>
       <c r="C62">
-        <v>-4.088587751469625</v>
+        <v>-4.265620222035981</v>
       </c>
       <c r="D62">
-        <v>3.671812248530374</v>
+        <v>3.624119777964018</v>
       </c>
       <c r="E62">
-        <v>7.326399999999999</v>
+        <v>7.45574</v>
       </c>
       <c r="F62">
-        <v>7.760399999999999</v>
+        <v>7.88974</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6359,37 +6359,37 @@
         <v>0.707</v>
       </c>
       <c r="M62">
-        <v>1.82990232</v>
+        <v>1.860400692</v>
       </c>
       <c r="N62">
-        <v>-1.12290232</v>
+        <v>-1.153400692</v>
       </c>
       <c r="O62">
-        <v>-0.1796643712</v>
+        <v>-0.18454411072</v>
       </c>
       <c r="P62">
-        <v>-0.9432379487999998</v>
+        <v>-0.96885658128</v>
       </c>
       <c r="Q62">
-        <v>-0.9272379487999998</v>
+        <v>-0.9528565812799999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1335366214202777</v>
+        <v>0.135786278379772</v>
       </c>
       <c r="T62">
-        <v>1.2077276183516</v>
+        <v>1.238694993181128</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06181750728639986</v>
+        <v>0.06080410552760641</v>
       </c>
       <c r="W62">
-        <v>0.2212234317818669</v>
+        <v>0.2214623919165904</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3863594205399992</v>
+        <v>0.3800256595475401</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1880487076372312</v>
+        <v>0.1899487076372312</v>
       </c>
       <c r="C63">
-        <v>-4.265620222035981</v>
+        <v>-4.44142964172836</v>
       </c>
       <c r="D63">
-        <v>3.624119777964018</v>
+        <v>3.577650358271639</v>
       </c>
       <c r="E63">
-        <v>7.45574</v>
+        <v>7.585079999999999</v>
       </c>
       <c r="F63">
-        <v>7.88974</v>
+        <v>8.019079999999999</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6441,37 +6441,37 @@
         <v>0.707</v>
       </c>
       <c r="M63">
-        <v>1.860400692</v>
+        <v>1.890899064</v>
       </c>
       <c r="N63">
-        <v>-1.153400692</v>
+        <v>-1.183899064</v>
       </c>
       <c r="O63">
-        <v>-0.18454411072</v>
+        <v>-0.18942385024</v>
       </c>
       <c r="P63">
-        <v>-0.96885658128</v>
+        <v>-0.9944752137599998</v>
       </c>
       <c r="Q63">
-        <v>-0.9528565812799999</v>
+        <v>-0.9784752137599998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.135786278379772</v>
+        <v>0.1381543383371345</v>
       </c>
       <c r="T63">
-        <v>1.238694993181128</v>
+        <v>1.27129222984379</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06080410552760641</v>
+        <v>0.05982339414812889</v>
       </c>
       <c r="W63">
-        <v>0.2214623919165904</v>
+        <v>0.2216936436598712</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3800256595475401</v>
+        <v>0.3738962134258056</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1899487076372312</v>
+        <v>0.1918487076372312</v>
       </c>
       <c r="C64">
-        <v>-4.44142964172836</v>
+        <v>-4.616062461779501</v>
       </c>
       <c r="D64">
-        <v>3.577650358271639</v>
+        <v>3.532357538220498</v>
       </c>
       <c r="E64">
-        <v>7.585079999999999</v>
+        <v>7.71442</v>
       </c>
       <c r="F64">
-        <v>8.019079999999999</v>
+        <v>8.14842</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6523,37 +6523,37 @@
         <v>0.707</v>
       </c>
       <c r="M64">
-        <v>1.890899064</v>
+        <v>1.921397436</v>
       </c>
       <c r="N64">
-        <v>-1.183899064</v>
+        <v>-1.214397436</v>
       </c>
       <c r="O64">
-        <v>-0.18942385024</v>
+        <v>-0.19430358976</v>
       </c>
       <c r="P64">
-        <v>-0.9944752137599998</v>
+        <v>-1.02009384624</v>
       </c>
       <c r="Q64">
-        <v>-0.9784752137599998</v>
+        <v>-1.00409384624</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1381543383371345</v>
+        <v>0.1406504015354354</v>
       </c>
       <c r="T64">
-        <v>1.27129222984379</v>
+        <v>1.305651479299027</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05982339414812889</v>
+        <v>0.05887381646323795</v>
       </c>
       <c r="W64">
-        <v>0.2216936436598712</v>
+        <v>0.2219175540779685</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3738962134258056</v>
+        <v>0.3679613528952372</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1918487076372312</v>
+        <v>0.1937487076372313</v>
       </c>
       <c r="C65">
-        <v>-4.616062461779501</v>
+        <v>-4.789562810551238</v>
       </c>
       <c r="D65">
-        <v>3.532357538220498</v>
+        <v>3.488197189448761</v>
       </c>
       <c r="E65">
-        <v>7.71442</v>
+        <v>7.843759999999999</v>
       </c>
       <c r="F65">
-        <v>8.14842</v>
+        <v>8.277759999999999</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6605,37 +6605,37 @@
         <v>0.707</v>
       </c>
       <c r="M65">
-        <v>1.921397436</v>
+        <v>1.951895808</v>
       </c>
       <c r="N65">
-        <v>-1.214397436</v>
+        <v>-1.244895808</v>
       </c>
       <c r="O65">
-        <v>-0.19430358976</v>
+        <v>-0.19918332928</v>
       </c>
       <c r="P65">
-        <v>-1.02009384624</v>
+        <v>-1.04571247872</v>
       </c>
       <c r="Q65">
-        <v>-1.00409384624</v>
+        <v>-1.02971247872</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1406504015354354</v>
+        <v>0.1432851349114197</v>
       </c>
       <c r="T65">
-        <v>1.305651479299027</v>
+        <v>1.341919575946223</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05887381646323795</v>
+        <v>0.05795391308099987</v>
       </c>
       <c r="W65">
-        <v>0.2219175540779685</v>
+        <v>0.2221344672955002</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3679613528952372</v>
+        <v>0.3622119567562492</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1937487076372313</v>
+        <v>0.1956487076372312</v>
       </c>
       <c r="C66">
-        <v>-4.789562810551238</v>
+        <v>-4.961972636940445</v>
       </c>
       <c r="D66">
-        <v>3.488197189448761</v>
+        <v>3.445127363059556</v>
       </c>
       <c r="E66">
-        <v>7.843759999999999</v>
+        <v>7.9731</v>
       </c>
       <c r="F66">
-        <v>8.277759999999999</v>
+        <v>8.4071</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6687,37 +6687,37 @@
         <v>0.707</v>
       </c>
       <c r="M66">
-        <v>1.951895808</v>
+        <v>1.98239418</v>
       </c>
       <c r="N66">
-        <v>-1.244895808</v>
+        <v>-1.27539418</v>
       </c>
       <c r="O66">
-        <v>-0.19918332928</v>
+        <v>-0.2040630688</v>
       </c>
       <c r="P66">
-        <v>-1.04571247872</v>
+        <v>-1.0713311112</v>
       </c>
       <c r="Q66">
-        <v>-1.02971247872</v>
+        <v>-1.0553311112</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1432851349114197</v>
+        <v>0.1460704244803174</v>
       </c>
       <c r="T66">
-        <v>1.341919575946223</v>
+        <v>1.380260135258972</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05795391308099987</v>
+        <v>0.05706231441821525</v>
       </c>
       <c r="W66">
-        <v>0.2221344672955002</v>
+        <v>0.2223447062601848</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3622119567562492</v>
+        <v>0.3566394651138453</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1956487076372312</v>
+        <v>0.1975487076372313</v>
       </c>
       <c r="C67">
-        <v>-4.961972636940445</v>
+        <v>-5.133331843290513</v>
       </c>
       <c r="D67">
-        <v>3.445127363059556</v>
+        <v>3.403108156709488</v>
       </c>
       <c r="E67">
-        <v>7.9731</v>
+        <v>8.102440000000001</v>
       </c>
       <c r="F67">
-        <v>8.4071</v>
+        <v>8.536440000000001</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6769,37 +6769,37 @@
         <v>0.707</v>
       </c>
       <c r="M67">
-        <v>1.98239418</v>
+        <v>2.012892552</v>
       </c>
       <c r="N67">
-        <v>-1.27539418</v>
+        <v>-1.305892552</v>
       </c>
       <c r="O67">
-        <v>-0.2040630688</v>
+        <v>-0.2089428083200001</v>
       </c>
       <c r="P67">
-        <v>-1.0713311112</v>
+        <v>-1.09694974368</v>
       </c>
       <c r="Q67">
-        <v>-1.0553311112</v>
+        <v>-1.08094974368</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1460704244803174</v>
+        <v>0.1490195546120915</v>
       </c>
       <c r="T67">
-        <v>1.380260135258972</v>
+        <v>1.420856021590118</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05706231441821525</v>
+        <v>0.05619773389672713</v>
       </c>
       <c r="W67">
-        <v>0.2223447062601848</v>
+        <v>0.2225485743471518</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3566394651138453</v>
+        <v>0.3512358368545445</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1975487076372313</v>
+        <v>0.1994487076372313</v>
       </c>
       <c r="C68">
-        <v>-5.133331843290513</v>
+        <v>-5.30367840869352</v>
       </c>
       <c r="D68">
-        <v>3.403108156709488</v>
+        <v>3.36210159130648</v>
       </c>
       <c r="E68">
-        <v>8.102440000000001</v>
+        <v>8.231780000000001</v>
       </c>
       <c r="F68">
-        <v>8.536440000000001</v>
+        <v>8.66578</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6851,37 +6851,37 @@
         <v>0.707</v>
       </c>
       <c r="M68">
-        <v>2.012892552</v>
+        <v>2.043390924</v>
       </c>
       <c r="N68">
-        <v>-1.305892552</v>
+        <v>-1.336390924</v>
       </c>
       <c r="O68">
-        <v>-0.2089428083200001</v>
+        <v>-0.21382254784</v>
       </c>
       <c r="P68">
-        <v>-1.09694974368</v>
+        <v>-1.12256837616</v>
       </c>
       <c r="Q68">
-        <v>-1.08094974368</v>
+        <v>-1.10656837616</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1490195546120915</v>
+        <v>0.152147419903367</v>
       </c>
       <c r="T68">
-        <v>1.420856021590118</v>
+        <v>1.463912264668607</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05619773389672713</v>
+        <v>0.05535896174901479</v>
       </c>
       <c r="W68">
-        <v>0.2225485743471518</v>
+        <v>0.2227463568195823</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3512358368545445</v>
+        <v>0.3459935109313423</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1994487076372313</v>
+        <v>0.2013487076372313</v>
       </c>
       <c r="C69">
-        <v>-5.30367840869352</v>
+        <v>-5.473048503484004</v>
       </c>
       <c r="D69">
-        <v>3.36210159130648</v>
+        <v>3.322071496515997</v>
       </c>
       <c r="E69">
-        <v>8.231780000000001</v>
+        <v>8.361120000000001</v>
       </c>
       <c r="F69">
-        <v>8.66578</v>
+        <v>8.795120000000001</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6933,37 +6933,37 @@
         <v>0.707</v>
       </c>
       <c r="M69">
-        <v>2.043390924</v>
+        <v>2.073889296</v>
       </c>
       <c r="N69">
-        <v>-1.336390924</v>
+        <v>-1.366889296000001</v>
       </c>
       <c r="O69">
-        <v>-0.21382254784</v>
+        <v>-0.2187022873600001</v>
       </c>
       <c r="P69">
-        <v>-1.12256837616</v>
+        <v>-1.14818700864</v>
       </c>
       <c r="Q69">
-        <v>-1.10656837616</v>
+        <v>-1.13218700864</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.152147419903367</v>
+        <v>0.1554707767753472</v>
       </c>
       <c r="T69">
-        <v>1.463912264668607</v>
+        <v>1.509659522939501</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05535896174901479</v>
+        <v>0.05454485937035281</v>
       </c>
       <c r="W69">
-        <v>0.2227463568195823</v>
+        <v>0.2229383221604708</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3459935109313423</v>
+        <v>0.340905371064705</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2013487076372313</v>
+        <v>0.2032487076372312</v>
       </c>
       <c r="C70">
-        <v>-5.473048503484004</v>
+        <v>-5.64147659564979</v>
       </c>
       <c r="D70">
-        <v>3.322071496515997</v>
+        <v>3.28298340435021</v>
       </c>
       <c r="E70">
-        <v>8.361120000000001</v>
+        <v>8.490460000000001</v>
       </c>
       <c r="F70">
-        <v>8.795120000000001</v>
+        <v>8.92446</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7015,37 +7015,37 @@
         <v>0.707</v>
       </c>
       <c r="M70">
-        <v>2.073889296</v>
+        <v>2.104387668</v>
       </c>
       <c r="N70">
-        <v>-1.366889296000001</v>
+        <v>-1.397387668</v>
       </c>
       <c r="O70">
-        <v>-0.2187022873600001</v>
+        <v>-0.2235820268800001</v>
       </c>
       <c r="P70">
-        <v>-1.14818700864</v>
+        <v>-1.17380564112</v>
       </c>
       <c r="Q70">
-        <v>-1.13218700864</v>
+        <v>-1.15780564112</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1554707767753472</v>
+        <v>0.1590085437681003</v>
       </c>
       <c r="T70">
-        <v>1.509659522939501</v>
+        <v>1.558358217227872</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05454485937035281</v>
+        <v>0.05375435416208682</v>
       </c>
       <c r="W70">
-        <v>0.2229383221604708</v>
+        <v>0.2231247232885799</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.340905371064705</v>
+        <v>0.3359647135130426</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2032487076372312</v>
+        <v>0.2051487076372313</v>
       </c>
       <c r="C71">
-        <v>-5.64147659564979</v>
+        <v>-5.808995549817903</v>
       </c>
       <c r="D71">
-        <v>3.28298340435021</v>
+        <v>3.244804450182098</v>
       </c>
       <c r="E71">
-        <v>8.490460000000001</v>
+        <v>8.619800000000001</v>
       </c>
       <c r="F71">
-        <v>8.92446</v>
+        <v>9.053800000000001</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7097,37 +7097,37 @@
         <v>0.707</v>
       </c>
       <c r="M71">
-        <v>2.104387668</v>
+        <v>2.13488604</v>
       </c>
       <c r="N71">
-        <v>-1.397387668</v>
+        <v>-1.42788604</v>
       </c>
       <c r="O71">
-        <v>-0.2235820268800001</v>
+        <v>-0.2284617664</v>
       </c>
       <c r="P71">
-        <v>-1.17380564112</v>
+        <v>-1.1994242736</v>
       </c>
       <c r="Q71">
-        <v>-1.15780564112</v>
+        <v>-1.1834242736</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1590085437681003</v>
+        <v>0.1627821618937037</v>
       </c>
       <c r="T71">
-        <v>1.558358217227872</v>
+        <v>1.610303491135467</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05375435416208682</v>
+        <v>0.05298643481691416</v>
       </c>
       <c r="W71">
-        <v>0.2231247232885799</v>
+        <v>0.2233057986701717</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3359647135130426</v>
+        <v>0.3311652176057134</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2051487076372313</v>
+        <v>0.2070487076372313</v>
       </c>
       <c r="C72">
-        <v>-5.808995549817903</v>
+        <v>-5.975636719413011</v>
       </c>
       <c r="D72">
-        <v>3.244804450182098</v>
+        <v>3.207503280586989</v>
       </c>
       <c r="E72">
-        <v>8.619800000000001</v>
+        <v>8.749140000000001</v>
       </c>
       <c r="F72">
-        <v>9.053800000000001</v>
+        <v>9.18314</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7179,37 +7179,37 @@
         <v>0.707</v>
       </c>
       <c r="M72">
-        <v>2.13488604</v>
+        <v>2.165384412</v>
       </c>
       <c r="N72">
-        <v>-1.42788604</v>
+        <v>-1.458384412</v>
       </c>
       <c r="O72">
-        <v>-0.2284617664</v>
+        <v>-0.23334150592</v>
       </c>
       <c r="P72">
-        <v>-1.1994242736</v>
+        <v>-1.22504290608</v>
       </c>
       <c r="Q72">
-        <v>-1.1834242736</v>
+        <v>-1.20904290608</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1627821618937037</v>
+        <v>0.1668160295452107</v>
       </c>
       <c r="T72">
-        <v>1.610303491135467</v>
+        <v>1.665831197726346</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05298643481691416</v>
+        <v>0.05224014700259143</v>
       </c>
       <c r="W72">
-        <v>0.2233057986701717</v>
+        <v>0.223481773336789</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3311652176057134</v>
+        <v>0.3265009187661964</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2070487076372313</v>
+        <v>0.2089487076372312</v>
       </c>
       <c r="C73">
-        <v>-5.975636719413011</v>
+        <v>-6.141430032531607</v>
       </c>
       <c r="D73">
-        <v>3.207503280586989</v>
+        <v>3.171049967468392</v>
       </c>
       <c r="E73">
-        <v>8.749140000000001</v>
+        <v>8.87848</v>
       </c>
       <c r="F73">
-        <v>9.18314</v>
+        <v>9.312479999999999</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7261,37 +7261,37 @@
         <v>0.707</v>
       </c>
       <c r="M73">
-        <v>2.165384412</v>
+        <v>2.195882784</v>
       </c>
       <c r="N73">
-        <v>-1.458384412</v>
+        <v>-1.488882784</v>
       </c>
       <c r="O73">
-        <v>-0.23334150592</v>
+        <v>-0.23822124544</v>
       </c>
       <c r="P73">
-        <v>-1.22504290608</v>
+        <v>-1.25066153856</v>
       </c>
       <c r="Q73">
-        <v>-1.20904290608</v>
+        <v>-1.23466153856</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1668160295452107</v>
+        <v>0.1711380306003968</v>
       </c>
       <c r="T73">
-        <v>1.665831197726345</v>
+        <v>1.725325169073715</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05224014700259143</v>
+        <v>0.05151458940533321</v>
       </c>
       <c r="W73">
-        <v>0.223481773336789</v>
+        <v>0.2236528598182224</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3265009187661964</v>
+        <v>0.3219661837833325</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2089487076372312</v>
+        <v>0.2108487076372313</v>
       </c>
       <c r="C74">
-        <v>-6.141430032531607</v>
+        <v>-6.306404072026199</v>
       </c>
       <c r="D74">
-        <v>3.171049967468392</v>
+        <v>3.135415927973801</v>
       </c>
       <c r="E74">
-        <v>8.87848</v>
+        <v>9.007820000000001</v>
       </c>
       <c r="F74">
-        <v>9.312479999999999</v>
+        <v>9.44182</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7343,37 +7343,37 @@
         <v>0.707</v>
       </c>
       <c r="M74">
-        <v>2.195882784</v>
+        <v>2.226381156</v>
       </c>
       <c r="N74">
-        <v>-1.488882784</v>
+        <v>-1.519381156</v>
       </c>
       <c r="O74">
-        <v>-0.23822124544</v>
+        <v>-0.24310098496</v>
       </c>
       <c r="P74">
-        <v>-1.25066153856</v>
+        <v>-1.27628017104</v>
       </c>
       <c r="Q74">
-        <v>-1.23466153856</v>
+        <v>-1.26028017104</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1711380306003968</v>
+        <v>0.175780179881893</v>
       </c>
       <c r="T74">
-        <v>1.725325169073715</v>
+        <v>1.78922610126163</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05151458940533321</v>
+        <v>0.05080891009841084</v>
       </c>
       <c r="W74">
-        <v>0.2236528598182224</v>
+        <v>0.2238192589987947</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3219661837833325</v>
+        <v>0.3175556881150677</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2108487076372313</v>
+        <v>0.2127487076372312</v>
       </c>
       <c r="C75">
-        <v>-6.306404072026199</v>
+        <v>-6.470586150249928</v>
       </c>
       <c r="D75">
-        <v>3.135415927973801</v>
+        <v>3.100573849750071</v>
       </c>
       <c r="E75">
-        <v>9.007820000000001</v>
+        <v>9.13716</v>
       </c>
       <c r="F75">
-        <v>9.44182</v>
+        <v>9.571159999999999</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7425,37 +7425,37 @@
         <v>0.707</v>
       </c>
       <c r="M75">
-        <v>2.226381156</v>
+        <v>2.256879528</v>
       </c>
       <c r="N75">
-        <v>-1.519381156</v>
+        <v>-1.549879528</v>
       </c>
       <c r="O75">
-        <v>-0.24310098496</v>
+        <v>-0.24798072448</v>
       </c>
       <c r="P75">
-        <v>-1.27628017104</v>
+        <v>-1.30189880352</v>
       </c>
       <c r="Q75">
-        <v>-1.26028017104</v>
+        <v>-1.28589880352</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.175780179881893</v>
+        <v>0.1807794175696581</v>
       </c>
       <c r="T75">
-        <v>1.78922610126163</v>
+        <v>1.858042489771693</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05080891009841084</v>
+        <v>0.05012230320518907</v>
       </c>
       <c r="W75">
-        <v>0.2238192589987947</v>
+        <v>0.2239811609042164</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3175556881150677</v>
+        <v>0.3132643950324316</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2127487076372312</v>
+        <v>0.2146487076372313</v>
       </c>
       <c r="C76">
-        <v>-6.470586150249928</v>
+        <v>-6.634002378872411</v>
       </c>
       <c r="D76">
-        <v>3.100573849750071</v>
+        <v>3.066497621127589</v>
       </c>
       <c r="E76">
-        <v>9.13716</v>
+        <v>9.266500000000001</v>
       </c>
       <c r="F76">
-        <v>9.571159999999999</v>
+        <v>9.7005</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7507,37 +7507,37 @@
         <v>0.707</v>
       </c>
       <c r="M76">
-        <v>2.256879528</v>
+        <v>2.2873779</v>
       </c>
       <c r="N76">
-        <v>-1.549879528</v>
+        <v>-1.5803779</v>
       </c>
       <c r="O76">
-        <v>-0.24798072448</v>
+        <v>-0.2528604640000001</v>
       </c>
       <c r="P76">
-        <v>-1.30189880352</v>
+        <v>-1.327517436</v>
       </c>
       <c r="Q76">
-        <v>-1.28589880352</v>
+        <v>-1.311517436</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1807794175696581</v>
+        <v>0.1861785942724444</v>
       </c>
       <c r="T76">
-        <v>1.858042489771693</v>
+        <v>1.93236418936256</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05012230320518907</v>
+        <v>0.04945400582911989</v>
       </c>
       <c r="W76">
-        <v>0.2239811609042164</v>
+        <v>0.2241387454254936</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3132643950324316</v>
+        <v>0.3090875364319992</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2146487076372313</v>
+        <v>0.2165487076372312</v>
       </c>
       <c r="C77">
-        <v>-6.634002378872411</v>
+        <v>-6.796677734141823</v>
       </c>
       <c r="D77">
-        <v>3.066497621127589</v>
+        <v>3.033162265858176</v>
       </c>
       <c r="E77">
-        <v>9.266500000000001</v>
+        <v>9.39584</v>
       </c>
       <c r="F77">
-        <v>9.7005</v>
+        <v>9.829839999999999</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7589,37 +7589,37 @@
         <v>0.707</v>
       </c>
       <c r="M77">
-        <v>2.2873779</v>
+        <v>2.317876272</v>
       </c>
       <c r="N77">
-        <v>-1.5803779</v>
+        <v>-1.610876272</v>
       </c>
       <c r="O77">
-        <v>-0.2528604640000001</v>
+        <v>-0.25774020352</v>
       </c>
       <c r="P77">
-        <v>-1.327517436</v>
+        <v>-1.35313606848</v>
       </c>
       <c r="Q77">
-        <v>-1.311517436</v>
+        <v>-1.33713606848</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1861785942724444</v>
+        <v>0.1920277023671296</v>
       </c>
       <c r="T77">
-        <v>1.93236418936256</v>
+        <v>2.012879363919334</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04945400582911989</v>
+        <v>0.04880329522610515</v>
       </c>
       <c r="W77">
-        <v>0.2241387454254936</v>
+        <v>0.2242921829856844</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3090875364319992</v>
+        <v>0.3050205951631572</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2165487076372312</v>
+        <v>0.2184487076372313</v>
       </c>
       <c r="C78">
-        <v>-6.796677734141823</v>
+        <v>-6.958636117936064</v>
       </c>
       <c r="D78">
-        <v>3.033162265858176</v>
+        <v>3.000543882063936</v>
       </c>
       <c r="E78">
-        <v>9.39584</v>
+        <v>9.525180000000001</v>
       </c>
       <c r="F78">
-        <v>9.829839999999999</v>
+        <v>9.95918</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7671,37 +7671,37 @@
         <v>0.707</v>
       </c>
       <c r="M78">
-        <v>2.317876272</v>
+        <v>2.348374644</v>
       </c>
       <c r="N78">
-        <v>-1.610876272</v>
+        <v>-1.641374644</v>
       </c>
       <c r="O78">
-        <v>-0.25774020352</v>
+        <v>-0.2626199430400001</v>
       </c>
       <c r="P78">
-        <v>-1.35313606848</v>
+        <v>-1.37875470096</v>
       </c>
       <c r="Q78">
-        <v>-1.33713606848</v>
+        <v>-1.36275470096</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1920277023671296</v>
+        <v>0.1983854285570048</v>
       </c>
       <c r="T78">
-        <v>2.012879363919334</v>
+        <v>2.100395858002784</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04880329522610515</v>
+        <v>0.04816948619719469</v>
       </c>
       <c r="W78">
-        <v>0.2242921829856844</v>
+        <v>0.2244416351547015</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3050205951631572</v>
+        <v>0.3010592887324668</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2184487076372313</v>
+        <v>0.2203487076372312</v>
       </c>
       <c r="C79">
-        <v>-6.958636117936064</v>
+        <v>-7.119900414916578</v>
       </c>
       <c r="D79">
-        <v>3.000543882063936</v>
+        <v>2.968619585083421</v>
       </c>
       <c r="E79">
-        <v>9.525180000000001</v>
+        <v>9.65452</v>
       </c>
       <c r="F79">
-        <v>9.95918</v>
+        <v>10.08852</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7753,37 +7753,37 @@
         <v>0.707</v>
       </c>
       <c r="M79">
-        <v>2.348374644</v>
+        <v>2.378873016</v>
       </c>
       <c r="N79">
-        <v>-1.641374644</v>
+        <v>-1.671873016</v>
       </c>
       <c r="O79">
-        <v>-0.2626199430400001</v>
+        <v>-0.26749968256</v>
       </c>
       <c r="P79">
-        <v>-1.37875470096</v>
+        <v>-1.40437333344</v>
       </c>
       <c r="Q79">
-        <v>-1.36275470096</v>
+        <v>-1.38837333344</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1983854285570048</v>
+        <v>0.2053211298550505</v>
       </c>
       <c r="T79">
-        <v>2.100395858002784</v>
+        <v>2.19586839700291</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04816948619719469</v>
+        <v>0.04755192868184605</v>
       </c>
       <c r="W79">
-        <v>0.2244416351547015</v>
+        <v>0.2245872552168207</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3010592887324668</v>
+        <v>0.2971995542615377</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2203487076372312</v>
+        <v>0.2222487076372313</v>
       </c>
       <c r="C80">
-        <v>-7.119900414916578</v>
+        <v>-7.280492546072079</v>
       </c>
       <c r="D80">
-        <v>2.968619585083421</v>
+        <v>2.937367453927921</v>
       </c>
       <c r="E80">
-        <v>9.65452</v>
+        <v>9.783860000000001</v>
       </c>
       <c r="F80">
-        <v>10.08852</v>
+        <v>10.21786</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7835,37 +7835,37 @@
         <v>0.707</v>
       </c>
       <c r="M80">
-        <v>2.378873016</v>
+        <v>2.409371388</v>
       </c>
       <c r="N80">
-        <v>-1.671873016</v>
+        <v>-1.702371388</v>
       </c>
       <c r="O80">
-        <v>-0.26749968256</v>
+        <v>-0.2723794220800001</v>
       </c>
       <c r="P80">
-        <v>-1.40437333344</v>
+        <v>-1.42999196592</v>
       </c>
       <c r="Q80">
-        <v>-1.38837333344</v>
+        <v>-1.41399196592</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2053211298550505</v>
+        <v>0.2129173741338624</v>
       </c>
       <c r="T80">
-        <v>2.19586839700291</v>
+        <v>2.300433558764953</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04755192868184605</v>
+        <v>0.04695000553397456</v>
       </c>
       <c r="W80">
-        <v>0.2245872552168207</v>
+        <v>0.2247291886950888</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2971995542615377</v>
+        <v>0.293437534587341</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2222487076372313</v>
+        <v>0.2241487076372312</v>
       </c>
       <c r="C81">
-        <v>-7.280492546072079</v>
+        <v>-7.440433518915395</v>
       </c>
       <c r="D81">
-        <v>2.937367453927921</v>
+        <v>2.906766481084606</v>
       </c>
       <c r="E81">
-        <v>9.783860000000001</v>
+        <v>9.913200000000002</v>
       </c>
       <c r="F81">
-        <v>10.21786</v>
+        <v>10.3472</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7917,37 +7917,37 @@
         <v>0.707</v>
       </c>
       <c r="M81">
-        <v>2.409371388</v>
+        <v>2.43986976</v>
       </c>
       <c r="N81">
-        <v>-1.702371388</v>
+        <v>-1.73286976</v>
       </c>
       <c r="O81">
-        <v>-0.2723794220800001</v>
+        <v>-0.2772591616</v>
       </c>
       <c r="P81">
-        <v>-1.42999196592</v>
+        <v>-1.4556105984</v>
       </c>
       <c r="Q81">
-        <v>-1.41399196592</v>
+        <v>-1.4396105984</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2129173741338624</v>
+        <v>0.2212732428405555</v>
       </c>
       <c r="T81">
-        <v>2.300433558764953</v>
+        <v>2.415455236703201</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04695000553397456</v>
+        <v>0.04636313046479989</v>
       </c>
       <c r="W81">
-        <v>0.2247291886950888</v>
+        <v>0.2248675738364002</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.293437534587341</v>
+        <v>0.2897695654049992</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2241487076372312</v>
+        <v>0.2260487076372312</v>
       </c>
       <c r="C82">
-        <v>-7.440433518915395</v>
+        <v>-7.599743474575026</v>
       </c>
       <c r="D82">
-        <v>2.906766481084606</v>
+        <v>2.876796525424974</v>
       </c>
       <c r="E82">
-        <v>9.913200000000002</v>
+        <v>10.04254</v>
       </c>
       <c r="F82">
-        <v>10.3472</v>
+        <v>10.47654</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7999,37 +7999,37 @@
         <v>0.707</v>
       </c>
       <c r="M82">
-        <v>2.43986976</v>
+        <v>2.470368132</v>
       </c>
       <c r="N82">
-        <v>-1.73286976</v>
+        <v>-1.763368132</v>
       </c>
       <c r="O82">
-        <v>-0.2772591616</v>
+        <v>-0.28213890112</v>
       </c>
       <c r="P82">
-        <v>-1.4556105984</v>
+        <v>-1.48122923088</v>
       </c>
       <c r="Q82">
-        <v>-1.4396105984</v>
+        <v>-1.46522923088</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2212732428405555</v>
+        <v>0.230508676674269</v>
       </c>
       <c r="T82">
-        <v>2.415455236703201</v>
+        <v>2.54258445968758</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04636313046479989</v>
+        <v>0.04579074613807396</v>
       </c>
       <c r="W82">
-        <v>0.2248675738364002</v>
+        <v>0.2250025420606422</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2897695654049992</v>
+        <v>0.2861921633629623</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2260487076372312</v>
+        <v>0.2279487076372313</v>
       </c>
       <c r="C83">
-        <v>-7.599743474575026</v>
+        <v>-7.758441732003249</v>
       </c>
       <c r="D83">
-        <v>2.876796525424974</v>
+        <v>2.847438267996752</v>
       </c>
       <c r="E83">
-        <v>10.04254</v>
+        <v>10.17188</v>
       </c>
       <c r="F83">
-        <v>10.47654</v>
+        <v>10.60588</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8081,37 +8081,37 @@
         <v>0.707</v>
       </c>
       <c r="M83">
-        <v>2.470368132</v>
+        <v>2.500866504</v>
       </c>
       <c r="N83">
-        <v>-1.763368132</v>
+        <v>-1.793866504</v>
       </c>
       <c r="O83">
-        <v>-0.28213890112</v>
+        <v>-0.28701864064</v>
       </c>
       <c r="P83">
-        <v>-1.48122923088</v>
+        <v>-1.50684786336</v>
       </c>
       <c r="Q83">
-        <v>-1.46522923088</v>
+        <v>-1.49084786336</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.230508676674269</v>
+        <v>0.2407702698228395</v>
       </c>
       <c r="T83">
-        <v>2.54258445968758</v>
+        <v>2.683839151892446</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04579074613807396</v>
+        <v>0.04523232240468282</v>
       </c>
       <c r="W83">
-        <v>0.2250025420606422</v>
+        <v>0.2251342183769758</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2861921633629623</v>
+        <v>0.2827020150292675</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2279487076372313</v>
+        <v>0.2298487076372313</v>
       </c>
       <c r="C84">
-        <v>-7.758441732003249</v>
+        <v>-7.916546829504608</v>
       </c>
       <c r="D84">
-        <v>2.847438267996752</v>
+        <v>2.818673170495392</v>
       </c>
       <c r="E84">
-        <v>10.17188</v>
+        <v>10.30122</v>
       </c>
       <c r="F84">
-        <v>10.60588</v>
+        <v>10.73522</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8163,37 +8163,37 @@
         <v>0.707</v>
       </c>
       <c r="M84">
-        <v>2.500866504</v>
+        <v>2.531364876</v>
       </c>
       <c r="N84">
-        <v>-1.793866504</v>
+        <v>-1.824364876</v>
       </c>
       <c r="O84">
-        <v>-0.28701864064</v>
+        <v>-0.29189838016</v>
       </c>
       <c r="P84">
-        <v>-1.50684786336</v>
+        <v>-1.53246649584</v>
       </c>
       <c r="Q84">
-        <v>-1.49084786336</v>
+        <v>-1.51646649584</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2407702698228395</v>
+        <v>0.252239109224183</v>
       </c>
       <c r="T84">
-        <v>2.683839151892446</v>
+        <v>2.841712043180237</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04523232240468282</v>
+        <v>0.04468735466486736</v>
       </c>
       <c r="W84">
-        <v>0.2251342183769758</v>
+        <v>0.2252627217700243</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2827020150292675</v>
+        <v>0.279295966655421</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2298487076372313</v>
+        <v>0.2317487076372313</v>
       </c>
       <c r="C85">
-        <v>-7.916546829504608</v>
+        <v>-8.074076563772486</v>
       </c>
       <c r="D85">
-        <v>2.818673170495392</v>
+        <v>2.790483436227515</v>
       </c>
       <c r="E85">
-        <v>10.30122</v>
+        <v>10.43056</v>
       </c>
       <c r="F85">
-        <v>10.73522</v>
+        <v>10.86456</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8245,37 +8245,37 @@
         <v>0.707</v>
       </c>
       <c r="M85">
-        <v>2.531364876</v>
+        <v>2.561863248</v>
       </c>
       <c r="N85">
-        <v>-1.824364876</v>
+        <v>-1.854863248</v>
       </c>
       <c r="O85">
-        <v>-0.29189838016</v>
+        <v>-0.2967781196800001</v>
       </c>
       <c r="P85">
-        <v>-1.53246649584</v>
+        <v>-1.55808512832</v>
       </c>
       <c r="Q85">
-        <v>-1.51646649584</v>
+        <v>-1.54208512832</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.252239109224183</v>
+        <v>0.2651415535506945</v>
       </c>
       <c r="T85">
-        <v>2.841712043180237</v>
+        <v>3.019319045879003</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04468735466486736</v>
+        <v>0.04415536234742846</v>
       </c>
       <c r="W85">
-        <v>0.2252627217700243</v>
+        <v>0.2253881655584764</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.279295966655421</v>
+        <v>0.2759710146714278</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2317487076372313</v>
+        <v>0.2336487076372313</v>
       </c>
       <c r="C86">
-        <v>-8.074076563772485</v>
+        <v>-8.231048026606381</v>
       </c>
       <c r="D86">
-        <v>2.790483436227515</v>
+        <v>2.762851973393618</v>
       </c>
       <c r="E86">
-        <v>10.43056</v>
+        <v>10.5599</v>
       </c>
       <c r="F86">
-        <v>10.86456</v>
+        <v>10.9939</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8327,37 +8327,37 @@
         <v>0.707</v>
       </c>
       <c r="M86">
-        <v>2.561863248</v>
+        <v>2.59236162</v>
       </c>
       <c r="N86">
-        <v>-1.854863248</v>
+        <v>-1.88536162</v>
       </c>
       <c r="O86">
-        <v>-0.29677811968</v>
+        <v>-0.3016578592</v>
       </c>
       <c r="P86">
-        <v>-1.55808512832</v>
+        <v>-1.5837037608</v>
       </c>
       <c r="Q86">
-        <v>-1.54208512832</v>
+        <v>-1.5677037608</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2651415535506944</v>
+        <v>0.2797643237874073</v>
       </c>
       <c r="T86">
-        <v>3.019319045879</v>
+        <v>3.220606982270934</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04415536234742847</v>
+        <v>0.04363588749628226</v>
       </c>
       <c r="W86">
-        <v>0.2253881655584764</v>
+        <v>0.2255106577283767</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2759710146714279</v>
+        <v>0.272724296851764</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2336487076372313</v>
+        <v>0.2355487076372313</v>
       </c>
       <c r="C87">
-        <v>-8.231048026606381</v>
+        <v>-8.387477639469155</v>
       </c>
       <c r="D87">
-        <v>2.762851973393618</v>
+        <v>2.735762360530844</v>
       </c>
       <c r="E87">
-        <v>10.5599</v>
+        <v>10.68924</v>
       </c>
       <c r="F87">
-        <v>10.9939</v>
+        <v>11.12324</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8409,37 +8409,37 @@
         <v>0.707</v>
       </c>
       <c r="M87">
-        <v>2.59236162</v>
+        <v>2.622859992</v>
       </c>
       <c r="N87">
-        <v>-1.88536162</v>
+        <v>-1.915859992</v>
       </c>
       <c r="O87">
-        <v>-0.3016578592</v>
+        <v>-0.30653759872</v>
       </c>
       <c r="P87">
-        <v>-1.5837037608</v>
+        <v>-1.60932239328</v>
       </c>
       <c r="Q87">
-        <v>-1.5677037608</v>
+        <v>-1.59332239328</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2797643237874073</v>
+        <v>0.2964760612007936</v>
       </c>
       <c r="T87">
-        <v>3.220606982270934</v>
+        <v>3.450650338147429</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04363588749628226</v>
+        <v>0.0431284934556278</v>
       </c>
       <c r="W87">
-        <v>0.2255106577283767</v>
+        <v>0.225630301243163</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.272724296851764</v>
+        <v>0.2695530840976738</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2355487076372313</v>
+        <v>0.2374487076372312</v>
       </c>
       <c r="C88">
-        <v>-8.387477639469155</v>
+        <v>-8.543381186030992</v>
       </c>
       <c r="D88">
-        <v>2.735762360530844</v>
+        <v>2.709198813969008</v>
       </c>
       <c r="E88">
-        <v>10.68924</v>
+        <v>10.81858</v>
       </c>
       <c r="F88">
-        <v>11.12324</v>
+        <v>11.25258</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8491,37 +8491,37 @@
         <v>0.707</v>
       </c>
       <c r="M88">
-        <v>2.622859992</v>
+        <v>2.653358364</v>
       </c>
       <c r="N88">
-        <v>-1.915859992</v>
+        <v>-1.946358364</v>
       </c>
       <c r="O88">
-        <v>-0.30653759872</v>
+        <v>-0.3114173382400001</v>
       </c>
       <c r="P88">
-        <v>-1.60932239328</v>
+        <v>-1.63494102576</v>
       </c>
       <c r="Q88">
-        <v>-1.59332239328</v>
+        <v>-1.61894102576</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2964760612007936</v>
+        <v>0.3157588351393161</v>
       </c>
       <c r="T88">
-        <v>3.450650338147429</v>
+        <v>3.716084979543385</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0431284934556278</v>
+        <v>0.04263276364579299</v>
       </c>
       <c r="W88">
-        <v>0.225630301243163</v>
+        <v>0.225747194332322</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2695530840976738</v>
+        <v>0.2664547727862062</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2374487076372312</v>
+        <v>0.2393487076372312</v>
       </c>
       <c r="C89">
-        <v>-8.543381186030992</v>
+        <v>-8.698773842835664</v>
       </c>
       <c r="D89">
-        <v>2.709198813969008</v>
+        <v>2.683146157164336</v>
       </c>
       <c r="E89">
-        <v>10.81858</v>
+        <v>10.94792</v>
       </c>
       <c r="F89">
-        <v>11.25258</v>
+        <v>11.38192</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8573,37 +8573,37 @@
         <v>0.707</v>
       </c>
       <c r="M89">
-        <v>2.653358364</v>
+        <v>2.683856736</v>
       </c>
       <c r="N89">
-        <v>-1.946358364</v>
+        <v>-1.976856736</v>
       </c>
       <c r="O89">
-        <v>-0.3114173382400001</v>
+        <v>-0.31629707776</v>
       </c>
       <c r="P89">
-        <v>-1.63494102576</v>
+        <v>-1.66055965824</v>
       </c>
       <c r="Q89">
-        <v>-1.61894102576</v>
+        <v>-1.64455965824</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3157588351393161</v>
+        <v>0.3382554047342592</v>
       </c>
       <c r="T89">
-        <v>3.716084979543385</v>
+        <v>4.025758727838668</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04263276364579299</v>
+        <v>0.04214830042254535</v>
       </c>
       <c r="W89">
-        <v>0.225747194332322</v>
+        <v>0.2258614307603638</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2664547727862062</v>
+        <v>0.2634268776409084</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2393487076372312</v>
+        <v>0.2412487076372312</v>
       </c>
       <c r="C90">
-        <v>-8.698773842835664</v>
+        <v>-8.853670208214238</v>
       </c>
       <c r="D90">
-        <v>2.683146157164336</v>
+        <v>2.657589791785762</v>
       </c>
       <c r="E90">
-        <v>10.94792</v>
+        <v>11.07726</v>
       </c>
       <c r="F90">
-        <v>11.38192</v>
+        <v>11.51126</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8655,37 +8655,37 @@
         <v>0.707</v>
       </c>
       <c r="M90">
-        <v>2.683856736</v>
+        <v>2.714355108</v>
       </c>
       <c r="N90">
-        <v>-1.976856736</v>
+        <v>-2.007355108</v>
       </c>
       <c r="O90">
-        <v>-0.31629707776</v>
+        <v>-0.32117681728</v>
       </c>
       <c r="P90">
-        <v>-1.66055965824</v>
+        <v>-1.68617829072</v>
       </c>
       <c r="Q90">
-        <v>-1.64455965824</v>
+        <v>-1.67017829072</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3382554047342592</v>
+        <v>0.3648422597101009</v>
       </c>
       <c r="T90">
-        <v>4.025758727838668</v>
+        <v>4.39173679400582</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04214830042254535</v>
+        <v>0.04167472401330327</v>
       </c>
       <c r="W90">
-        <v>0.2258614307603638</v>
+        <v>0.2259731000776631</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2634268776409084</v>
+        <v>0.2604670250831455</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2412487076372312</v>
+        <v>0.2431487076372313</v>
       </c>
       <c r="C91">
-        <v>-8.853670208214238</v>
+        <v>-9.008084329562006</v>
       </c>
       <c r="D91">
-        <v>2.657589791785762</v>
+        <v>2.632515670437992</v>
       </c>
       <c r="E91">
-        <v>11.07726</v>
+        <v>11.2066</v>
       </c>
       <c r="F91">
-        <v>11.51126</v>
+        <v>11.6406</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8737,37 +8737,37 @@
         <v>0.707</v>
       </c>
       <c r="M91">
-        <v>2.714355108</v>
+        <v>2.74485348</v>
       </c>
       <c r="N91">
-        <v>-2.007355108</v>
+        <v>-2.03785348</v>
       </c>
       <c r="O91">
-        <v>-0.32117681728</v>
+        <v>-0.3260565568</v>
       </c>
       <c r="P91">
-        <v>-1.68617829072</v>
+        <v>-1.7117969232</v>
       </c>
       <c r="Q91">
-        <v>-1.67017829072</v>
+        <v>-1.6957969232</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3648422597101009</v>
+        <v>0.396746485681111</v>
       </c>
       <c r="T91">
-        <v>4.39173679400582</v>
+        <v>4.830910473406402</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04167472401330327</v>
+        <v>0.04121167152426657</v>
       </c>
       <c r="W91">
-        <v>0.2259731000776631</v>
+        <v>0.226082287854578</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2604670250831455</v>
+        <v>0.257572947026666</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2431487076372313</v>
+        <v>0.2450487076372312</v>
       </c>
       <c r="C92">
-        <v>-9.008084329562006</v>
+        <v>-9.162029729085708</v>
       </c>
       <c r="D92">
-        <v>2.632515670437992</v>
+        <v>2.607910270914292</v>
       </c>
       <c r="E92">
-        <v>11.2066</v>
+        <v>11.33594</v>
       </c>
       <c r="F92">
-        <v>11.6406</v>
+        <v>11.76994</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8819,37 +8819,37 @@
         <v>0.707</v>
       </c>
       <c r="M92">
-        <v>2.74485348</v>
+        <v>2.775351852</v>
       </c>
       <c r="N92">
-        <v>-2.03785348</v>
+        <v>-2.068351852</v>
       </c>
       <c r="O92">
-        <v>-0.3260565568</v>
+        <v>-0.33093629632</v>
       </c>
       <c r="P92">
-        <v>-1.7117969232</v>
+        <v>-1.73741555568</v>
       </c>
       <c r="Q92">
-        <v>-1.6957969232</v>
+        <v>-1.72141555568</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.396746485681111</v>
+        <v>0.435740539645679</v>
       </c>
       <c r="T92">
-        <v>4.830910473406402</v>
+        <v>5.367678303784892</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04121167152426657</v>
+        <v>0.0407587960130109</v>
       </c>
       <c r="W92">
-        <v>0.226082287854578</v>
+        <v>0.226189075900132</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.257572947026666</v>
+        <v>0.254742475081318</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2450487076372312</v>
+        <v>0.2469487076372313</v>
       </c>
       <c r="C93">
-        <v>-9.162029729085708</v>
+        <v>-9.315519428120208</v>
       </c>
       <c r="D93">
-        <v>2.607910270914292</v>
+        <v>2.58376057187979</v>
       </c>
       <c r="E93">
-        <v>11.33594</v>
+        <v>11.46528</v>
       </c>
       <c r="F93">
-        <v>11.76994</v>
+        <v>11.89928</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8901,37 +8901,37 @@
         <v>0.707</v>
       </c>
       <c r="M93">
-        <v>2.775351852</v>
+        <v>2.805850224</v>
       </c>
       <c r="N93">
-        <v>-2.068351852</v>
+        <v>-2.098850224</v>
       </c>
       <c r="O93">
-        <v>-0.33093629632</v>
+        <v>-0.33581603584</v>
       </c>
       <c r="P93">
-        <v>-1.73741555568</v>
+        <v>-1.76303418816</v>
       </c>
       <c r="Q93">
-        <v>-1.72141555568</v>
+        <v>-1.74703418816</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.435740539645679</v>
+        <v>0.484483107101389</v>
       </c>
       <c r="T93">
-        <v>5.367678303784892</v>
+        <v>6.038638091758005</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0407587960130109</v>
+        <v>0.04031576562156513</v>
       </c>
       <c r="W93">
-        <v>0.226189075900132</v>
+        <v>0.226293542466435</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.254742475081318</v>
+        <v>0.2519735351347819</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2469487076372313</v>
+        <v>0.2488487076372312</v>
       </c>
       <c r="C94">
-        <v>-9.315519428120208</v>
+        <v>-9.46856597010653</v>
       </c>
       <c r="D94">
-        <v>2.58376057187979</v>
+        <v>2.56005402989347</v>
       </c>
       <c r="E94">
-        <v>11.46528</v>
+        <v>11.59462</v>
       </c>
       <c r="F94">
-        <v>11.89928</v>
+        <v>12.02862</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8983,37 +8983,37 @@
         <v>0.707</v>
       </c>
       <c r="M94">
-        <v>2.805850224</v>
+        <v>2.836348596</v>
       </c>
       <c r="N94">
-        <v>-2.098850224</v>
+        <v>-2.129348596</v>
       </c>
       <c r="O94">
-        <v>-0.33581603584</v>
+        <v>-0.3406957753600001</v>
       </c>
       <c r="P94">
-        <v>-1.76303418816</v>
+        <v>-1.78865282064</v>
       </c>
       <c r="Q94">
-        <v>-1.74703418816</v>
+        <v>-1.77265282064</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.484483107101389</v>
+        <v>0.5471521224015873</v>
       </c>
       <c r="T94">
-        <v>6.038638091758005</v>
+        <v>6.901300676294863</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04031576562156513</v>
+        <v>0.03988226276541926</v>
       </c>
       <c r="W94">
-        <v>0.226293542466435</v>
+        <v>0.2263957624399141</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2519735351347819</v>
+        <v>0.2492641422838703</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2488487076372312</v>
+        <v>0.2507487076372313</v>
       </c>
       <c r="C95">
-        <v>-9.46856597010653</v>
+        <v>-9.621181442316393</v>
       </c>
       <c r="D95">
-        <v>2.56005402989347</v>
+        <v>2.536778557683605</v>
       </c>
       <c r="E95">
-        <v>11.59462</v>
+        <v>11.72396</v>
       </c>
       <c r="F95">
-        <v>12.02862</v>
+        <v>12.15796</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9065,37 +9065,37 @@
         <v>0.707</v>
       </c>
       <c r="M95">
-        <v>2.836348596</v>
+        <v>2.866846968</v>
       </c>
       <c r="N95">
-        <v>-2.129348596</v>
+        <v>-2.159846968</v>
       </c>
       <c r="O95">
-        <v>-0.3406957753600001</v>
+        <v>-0.34557551488</v>
       </c>
       <c r="P95">
-        <v>-1.78865282064</v>
+        <v>-1.81427145312</v>
       </c>
       <c r="Q95">
-        <v>-1.77265282064</v>
+        <v>-1.79827145312</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5471521224015873</v>
+        <v>0.6307108094685189</v>
       </c>
       <c r="T95">
-        <v>6.901300676294863</v>
+        <v>8.051517455677343</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03988226276541926</v>
+        <v>0.03945798337429778</v>
       </c>
       <c r="W95">
-        <v>0.2263957624399141</v>
+        <v>0.2264958075203406</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2492641422838703</v>
+        <v>0.246612396089361</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2507487076372313</v>
+        <v>0.2526487076372313</v>
       </c>
       <c r="C96">
-        <v>-9.621181442316393</v>
+        <v>-9.773377496402359</v>
       </c>
       <c r="D96">
-        <v>2.536778557683605</v>
+        <v>2.513922503597641</v>
       </c>
       <c r="E96">
-        <v>11.72396</v>
+        <v>11.8533</v>
       </c>
       <c r="F96">
-        <v>12.15796</v>
+        <v>12.2873</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9147,37 +9147,37 @@
         <v>0.707</v>
       </c>
       <c r="M96">
-        <v>2.866846968</v>
+        <v>2.89734534</v>
       </c>
       <c r="N96">
-        <v>-2.159846968</v>
+        <v>-2.19034534</v>
       </c>
       <c r="O96">
-        <v>-0.34557551488</v>
+        <v>-0.3504552544000001</v>
       </c>
       <c r="P96">
-        <v>-1.81427145312</v>
+        <v>-1.8398900856</v>
       </c>
       <c r="Q96">
-        <v>-1.79827145312</v>
+        <v>-1.8238900856</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6307108094685189</v>
+        <v>0.7476929713622228</v>
       </c>
       <c r="T96">
-        <v>8.051517455677343</v>
+        <v>9.661820946812815</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03945798337429778</v>
+        <v>0.03904263618088411</v>
       </c>
       <c r="W96">
-        <v>0.2264958075203406</v>
+        <v>0.2265937463885475</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.246612396089361</v>
+        <v>0.2440164761305257</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2526487076372313</v>
+        <v>0.2545487076372313</v>
       </c>
       <c r="C97">
-        <v>-9.773377496402359</v>
+        <v>-9.92516536784696</v>
       </c>
       <c r="D97">
-        <v>2.513922503597641</v>
+        <v>2.491474632153042</v>
       </c>
       <c r="E97">
-        <v>11.8533</v>
+        <v>11.98264</v>
       </c>
       <c r="F97">
-        <v>12.2873</v>
+        <v>12.41664</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9229,37 +9229,37 @@
         <v>0.707</v>
       </c>
       <c r="M97">
-        <v>2.89734534</v>
+        <v>2.927843712</v>
       </c>
       <c r="N97">
-        <v>-2.19034534</v>
+        <v>-2.220843712000001</v>
       </c>
       <c r="O97">
-        <v>-0.3504552544000001</v>
+        <v>-0.3553349939200001</v>
       </c>
       <c r="P97">
-        <v>-1.8398900856</v>
+        <v>-1.865508718080001</v>
       </c>
       <c r="Q97">
-        <v>-1.8238900856</v>
+        <v>-1.849508718080001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7476929713622228</v>
+        <v>0.923166214202779</v>
       </c>
       <c r="T97">
-        <v>9.661820946812815</v>
+        <v>12.07727618351602</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03904263618088411</v>
+        <v>0.0386359420539999</v>
       </c>
       <c r="W97">
-        <v>0.2265937463885475</v>
+        <v>0.2266896448636668</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2440164761305257</v>
+        <v>0.2414746378374993</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2545487076372313</v>
+        <v>0.2564487076372313</v>
       </c>
       <c r="C98">
-        <v>-9.925165367846958</v>
+        <v>-10.07655589437904</v>
       </c>
       <c r="D98">
-        <v>2.491474632153042</v>
+        <v>2.469424105620961</v>
       </c>
       <c r="E98">
-        <v>11.98264</v>
+        <v>12.11198</v>
       </c>
       <c r="F98">
-        <v>12.41664</v>
+        <v>12.54598</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9311,37 +9311,37 @@
         <v>0.707</v>
       </c>
       <c r="M98">
-        <v>2.927843712</v>
+        <v>2.958342084</v>
       </c>
       <c r="N98">
-        <v>-2.220843712</v>
+        <v>-2.251342084</v>
       </c>
       <c r="O98">
-        <v>-0.3553349939200001</v>
+        <v>-0.36021473344</v>
       </c>
       <c r="P98">
-        <v>-1.86550871808</v>
+        <v>-1.89112735056</v>
       </c>
       <c r="Q98">
-        <v>-1.84950871808</v>
+        <v>-1.87512735056</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9231662142027767</v>
+        <v>1.215621618937036</v>
       </c>
       <c r="T98">
-        <v>12.07727618351599</v>
+        <v>16.10303491135466</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03863594205399991</v>
+        <v>0.03823763337303084</v>
       </c>
       <c r="W98">
-        <v>0.2266896448636668</v>
+        <v>0.2267835660506393</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2414746378374993</v>
+        <v>0.2389852085814427</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2564487076372313</v>
+        <v>0.2583487076372312</v>
       </c>
       <c r="C99">
-        <v>-10.07655589437904</v>
+        <v>-10.22755953342073</v>
       </c>
       <c r="D99">
-        <v>2.469424105620961</v>
+        <v>2.447760466579273</v>
       </c>
       <c r="E99">
-        <v>12.11198</v>
+        <v>12.24132</v>
       </c>
       <c r="F99">
-        <v>12.54598</v>
+        <v>12.67532</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9393,37 +9393,37 @@
         <v>0.707</v>
       </c>
       <c r="M99">
-        <v>2.958342084</v>
+        <v>2.988840456</v>
       </c>
       <c r="N99">
-        <v>-2.251342084</v>
+        <v>-2.281840456</v>
       </c>
       <c r="O99">
-        <v>-0.36021473344</v>
+        <v>-0.36509447296</v>
       </c>
       <c r="P99">
-        <v>-1.89112735056</v>
+        <v>-1.91674598304</v>
       </c>
       <c r="Q99">
-        <v>-1.87512735056</v>
+        <v>-1.90074598304</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.215621618937036</v>
+        <v>1.800532428405553</v>
       </c>
       <c r="T99">
-        <v>16.10303491135466</v>
+        <v>24.15455236703199</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03823763337303084</v>
+        <v>0.03784745344065297</v>
       </c>
       <c r="W99">
-        <v>0.2267835660506393</v>
+        <v>0.226875570478694</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2389852085814427</v>
+        <v>0.236546584004081</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2583487076372312</v>
+        <v>0.2602487076372312</v>
       </c>
       <c r="C100">
-        <v>-10.22755953342073</v>
+        <v>-10.37818637862403</v>
       </c>
       <c r="D100">
-        <v>2.447760466579273</v>
+        <v>2.426473621375968</v>
       </c>
       <c r="E100">
-        <v>12.24132</v>
+        <v>12.37066</v>
       </c>
       <c r="F100">
-        <v>12.67532</v>
+        <v>12.80466</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9475,37 +9475,37 @@
         <v>0.707</v>
       </c>
       <c r="M100">
-        <v>2.988840456</v>
+        <v>3.019338828</v>
       </c>
       <c r="N100">
-        <v>-2.281840456</v>
+        <v>-2.312338828</v>
       </c>
       <c r="O100">
-        <v>-0.36509447296</v>
+        <v>-0.36997421248</v>
       </c>
       <c r="P100">
-        <v>-1.91674598304</v>
+        <v>-1.94236461552</v>
       </c>
       <c r="Q100">
-        <v>-1.90074598304</v>
+        <v>-1.92636461552</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.800532428405553</v>
+        <v>3.555264856811107</v>
       </c>
       <c r="T100">
-        <v>24.15455236703199</v>
+        <v>48.30910473406397</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03784745344065297</v>
+        <v>0.03746515593115143</v>
       </c>
       <c r="W100">
-        <v>0.226875570478694</v>
+        <v>0.2269657162314345</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.236546584004081</v>
+        <v>0.2341572245696965</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2602487076372312</v>
-      </c>
-      <c r="C101">
-        <v>-10.37818637862403</v>
-      </c>
-      <c r="D101">
-        <v>2.426473621375968</v>
-      </c>
-      <c r="E101">
-        <v>12.37066</v>
-      </c>
-      <c r="F101">
-        <v>12.80466</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>12.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.723</v>
-      </c>
-      <c r="K101">
-        <v>0.016</v>
-      </c>
-      <c r="L101">
-        <v>0.707</v>
-      </c>
-      <c r="M101">
-        <v>3.019338828</v>
-      </c>
-      <c r="N101">
-        <v>-2.312338828</v>
-      </c>
-      <c r="O101">
-        <v>-0.36997421248</v>
-      </c>
-      <c r="P101">
-        <v>-1.94236461552</v>
-      </c>
-      <c r="Q101">
-        <v>-1.92636461552</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.555264856811107</v>
-      </c>
-      <c r="T101">
-        <v>48.30910473406397</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03746515593115143</v>
-      </c>
-      <c r="W101">
-        <v>0.2269657162314345</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2341572245696965</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
